--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -1,155 +1,279 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C14BE9D-9D2A-4C6C-8516-3C151EF70D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30195" yWindow="1395" windowWidth="27000" windowHeight="15735" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Res, Cap, Product" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$B$1:$P$17</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+  <si>
+    <t>KPI by FTE</t>
+  </si>
+  <si>
+    <t>Research Outputs</t>
+  </si>
+  <si>
+    <t>Training and Capacity Building</t>
+  </si>
+  <si>
+    <t>Product Development</t>
+  </si>
+  <si>
+    <t>Thomson indexed publications</t>
+  </si>
+  <si>
+    <t>Publications per IRS</t>
+  </si>
+  <si>
+    <t>High impact publications</t>
+  </si>
+  <si>
+    <t>PhD and MsC  students enrolled</t>
+  </si>
+  <si>
+    <t>PhD and MsC  theses completed</t>
+  </si>
+  <si>
+    <t>Stakeholders trained on innovations</t>
+  </si>
+  <si>
+    <t>Training to NARES by IITA Scientists</t>
+  </si>
+  <si>
+    <t>Varieties released</t>
+  </si>
+  <si>
+    <t>Genetic gain rate</t>
+  </si>
+  <si>
+    <t>Crop Trust compliance rate</t>
+  </si>
+  <si>
+    <t>Innovations in e-Catalogue</t>
+  </si>
+  <si>
+    <t>Innovations taken on by scaling partners</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Breeding</t>
+  </si>
+  <si>
+    <t>Genebanks</t>
+  </si>
+  <si>
+    <t>Seed System</t>
+  </si>
+  <si>
+    <t>RAFS</t>
+  </si>
+  <si>
+    <t>Plant Health</t>
+  </si>
+  <si>
+    <t>Farming Systems Agronomy</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>Mechanization</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>FIAS</t>
+  </si>
+  <si>
+    <t>GeYSI</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>VCMA</t>
+  </si>
+  <si>
+    <t>per Program Target (target/13)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="18"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.09997863704336681"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -548,380 +672,228 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="76">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="PR 1"/>
-      <sheetName val="PR 2"/>
-      <sheetName val="PR 3"/>
-      <sheetName val="PR 4"/>
-      <sheetName val="PR 5"/>
-      <sheetName val="PR 6"/>
-      <sheetName val="PR 7"/>
-      <sheetName val="PR 8"/>
-      <sheetName val="PR 9"/>
-      <sheetName val="PR 10"/>
-      <sheetName val="PR 11"/>
-      <sheetName val="PR 12"/>
-      <sheetName val="PR 13"/>
-      <sheetName val="PR 14"/>
-      <sheetName val="PR15"/>
-      <sheetName val="PR 16"/>
-      <sheetName val="PR 18"/>
-      <sheetName val="PR 19"/>
-      <sheetName val="PR20"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
-        <row r="4">
-          <cell r="G4">
-            <v>0.65217391304347827</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="4">
-          <cell r="G4">
-            <v>6.521739130434782E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="5">
-          <cell r="G5">
-            <v>0.25</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1240,900 +1212,757 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="B1:V22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="3.21875" customWidth="1" style="1" min="2" max="2"/>
-    <col width="24.77734375" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="6.21875" customWidth="1" style="1" min="4" max="8"/>
-    <col width="8.21875" customWidth="1" style="3" min="9" max="9"/>
-    <col width="8.6640625" customWidth="1" style="3" min="10" max="10"/>
-    <col width="6.21875" customWidth="1" style="3" min="11" max="11"/>
-    <col width="7.77734375" customWidth="1" style="3" min="12" max="12"/>
-    <col width="6.21875" customWidth="1" style="3" min="13" max="13"/>
-    <col width="7.77734375" customWidth="1" style="3" min="14" max="14"/>
-    <col width="6.21875" customWidth="1" style="3" min="15" max="15"/>
-    <col width="5.44140625" customWidth="1" style="3" min="16" max="16"/>
-    <col width="6.21875" customWidth="1" style="3" min="17" max="17"/>
-    <col width="8.21875" customWidth="1" style="3" min="18" max="22"/>
+    <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="6.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.77734375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="6.21875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="6.21875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="5.44140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="6.21875" style="3" customWidth="1"/>
+    <col min="18" max="22" width="8.21875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" thickBot="1">
-      <c r="C1" s="73" t="inlineStr">
-        <is>
-          <t>KPI by FTE</t>
-        </is>
-      </c>
-      <c r="D1" s="74" t="n"/>
-      <c r="E1" s="74" t="n"/>
-      <c r="F1" s="74" t="n"/>
-      <c r="G1" s="74" t="n"/>
-      <c r="H1" s="74" t="n"/>
-      <c r="I1" s="74" t="n"/>
-      <c r="J1" s="74" t="n"/>
-      <c r="K1" s="74" t="n"/>
-      <c r="L1" s="74" t="n"/>
-      <c r="M1" s="74" t="n"/>
-      <c r="N1" s="74" t="n"/>
-      <c r="O1" s="75" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
+    <row r="1" spans="2:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="64" t="inlineStr">
-        <is>
-          <t>Research Outputs</t>
-        </is>
-      </c>
-      <c r="E2" s="65" t="n"/>
-      <c r="F2" s="66" t="n"/>
-      <c r="G2" s="70" t="inlineStr">
-        <is>
-          <t>Training and Capacity Building</t>
-        </is>
-      </c>
-      <c r="H2" s="65" t="n"/>
-      <c r="I2" s="65" t="n"/>
-      <c r="J2" s="66" t="n"/>
-      <c r="K2" s="70" t="inlineStr">
-        <is>
-          <t>Product Development</t>
-        </is>
-      </c>
-      <c r="L2" s="65" t="n"/>
-      <c r="M2" s="65" t="n"/>
-      <c r="N2" s="65" t="n"/>
-      <c r="O2" s="66" t="n"/>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="6" t="n"/>
-      <c r="R2" s="7" t="n"/>
-      <c r="S2" s="7" t="n"/>
-      <c r="T2" s="7" t="n"/>
-      <c r="U2" s="7" t="n"/>
-      <c r="V2" s="7" t="n"/>
+    <row r="2" spans="2:22" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
     </row>
-    <row r="3" ht="143.55" customFormat="1" customHeight="1" s="17" thickBot="1">
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Thomson indexed publications</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Publications per IRS</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>High impact publications</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>PhD and MsC  students enrolled</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>PhD and MsC  theses completed</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Stakeholders trained on innovations</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>Training to NARES by IITA Scientists</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>Varieties released</t>
-        </is>
-      </c>
-      <c r="L3" s="14" t="inlineStr">
-        <is>
-          <t>Genetic gain rate</t>
-        </is>
-      </c>
-      <c r="M3" s="14" t="inlineStr">
-        <is>
-          <t>Crop Trust compliance rate</t>
-        </is>
-      </c>
-      <c r="N3" s="12" t="inlineStr">
-        <is>
-          <t>Innovations in e-Catalogue</t>
-        </is>
-      </c>
-      <c r="O3" s="13" t="inlineStr">
-        <is>
-          <t>Innovations taken on by scaling partners</t>
-        </is>
-      </c>
-      <c r="P3" s="15" t="n"/>
-      <c r="Q3" s="15" t="n"/>
-      <c r="R3" s="16" t="n"/>
-      <c r="S3" s="16" t="n"/>
-      <c r="T3" s="16" t="n"/>
-      <c r="U3" s="16" t="n"/>
-      <c r="V3" s="16" t="n"/>
+    <row r="3" spans="2:22" s="17" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
     </row>
-    <row r="4" ht="15.45" customHeight="1">
-      <c r="B4" s="67" t="inlineStr">
-        <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Biotech</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="n">
-        <v>3.142857142857143</v>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>0.4479591836734694</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="G4" s="19" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>9.714285714285714</v>
-      </c>
-      <c r="J4" s="23" t="n">
-        <v>26.28571428571428</v>
-      </c>
-      <c r="K4" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="22" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O4" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n"/>
+    <row r="4" spans="2:22" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="19">
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0.44795918367346937</v>
+      </c>
+      <c r="F4" s="21">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="G4" s="19">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="I4" s="22">
+        <v>9.7142857142857135</v>
+      </c>
+      <c r="J4" s="23">
+        <v>26.285714285714281</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="22">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="O4" s="23">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2"/>
     </row>
-    <row r="5" ht="15.6" customHeight="1">
-      <c r="B5" s="68" t="n"/>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Breeding</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>2.239130434782609</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>0.09725897920604916</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="25" t="n">
+    <row r="5" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="71"/>
+      <c r="C5" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="25">
+        <v>2.2391304347826089</v>
+      </c>
+      <c r="E5" s="26">
+        <v>9.7258979206049159E-2</v>
+      </c>
+      <c r="F5" s="27">
+        <v>0</v>
+      </c>
+      <c r="G5" s="25">
         <v>1.043478260869565</v>
       </c>
-      <c r="H5" s="28" t="n">
-        <v>1.217391304347826</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>4.695652173913044</v>
-      </c>
-      <c r="J5" s="29" t="n">
+      <c r="H5" s="28">
+        <v>1.2173913043478259</v>
+      </c>
+      <c r="I5" s="28">
+        <v>4.6956521739130439</v>
+      </c>
+      <c r="J5" s="29">
         <v>9.304347826086957</v>
       </c>
       <c r="K5" s="25">
-        <f>'[1]PR 8'!$G$4</f>
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="L5" s="28">
-        <f>'[1]PR 9'!$G$4</f>
-        <v/>
-      </c>
-      <c r="M5" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="28" t="n">
-        <v>0.3478260869565217</v>
-      </c>
-      <c r="O5" s="29" t="n">
-        <v>0.2173913043478261</v>
-      </c>
-      <c r="P5" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="28">
+        <v>0.34782608695652167</v>
+      </c>
+      <c r="O5" s="29">
+        <v>0.21739130434782611</v>
+      </c>
+      <c r="P5" s="2"/>
     </row>
-    <row r="6" ht="15.6" customHeight="1">
-      <c r="B6" s="68" t="n"/>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>Genebanks</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
+    <row r="6" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="71"/>
+      <c r="C6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="25">
         <v>1.25</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="26">
         <v>0.3125</v>
       </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="25" t="n">
+      <c r="F6" s="27">
+        <v>0</v>
+      </c>
+      <c r="G6" s="25">
         <v>6.5</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="28">
         <v>4.75</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="28">
         <v>1.25</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="29">
         <v>28.25</v>
       </c>
-      <c r="K6" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="K6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="M6" s="28">
-        <f>'[1]PR 10'!$G$5</f>
-        <v/>
-      </c>
-      <c r="N6" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="28">
+        <v>0</v>
+      </c>
+      <c r="O6" s="29">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2"/>
     </row>
-    <row r="7" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="69" t="n"/>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>Seed System</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>1.026666666666667</v>
-      </c>
-      <c r="E7" s="32" t="n">
-        <v>0.06844444444444445</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="H7" s="34" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="I7" s="34" t="n">
-        <v>149.8</v>
-      </c>
-      <c r="J7" s="35" t="n">
+    <row r="7" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="72"/>
+      <c r="C7" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="31">
+        <v>1.0266666666666671</v>
+      </c>
+      <c r="E7" s="32">
+        <v>6.8444444444444447E-2</v>
+      </c>
+      <c r="F7" s="33">
+        <v>0</v>
+      </c>
+      <c r="G7" s="31">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H7" s="34">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="I7" s="34">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="J7" s="35">
         <v>20.6</v>
       </c>
-      <c r="K7" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="34" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="O7" s="35" t="n">
+      <c r="K7" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="34">
+        <v>1.1333333333333331</v>
+      </c>
+      <c r="O7" s="35">
         <v>0.1333333333333333</v>
       </c>
-      <c r="P7" s="2" t="n"/>
+      <c r="P7" s="2"/>
     </row>
-    <row r="8" ht="15.6" customHeight="1">
-      <c r="B8" s="67" t="inlineStr">
-        <is>
-          <t>RAFS</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Plant Health</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>3.454166666666667</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>0.2878472222222223</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="G8" s="19" t="n">
+    <row r="8" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="19">
+        <v>3.4541666666666671</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0.28784722222222231</v>
+      </c>
+      <c r="F8" s="21">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G8" s="19">
         <v>0.75</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="22">
         <v>0.75</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="22">
         <v>8.5</v>
       </c>
-      <c r="J8" s="23" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="22" t="n">
+      <c r="J8" s="23">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="22">
         <v>0.5</v>
       </c>
-      <c r="O8" s="23" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="P8" s="2" t="n"/>
+      <c r="O8" s="23">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="P8" s="2"/>
     </row>
-    <row r="9" ht="15.6" customHeight="1">
-      <c r="B9" s="68" t="n"/>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>Farming Systems Agronomy</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>1.0435</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>0.05217500000000001</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H9" s="28" t="n">
+    <row r="9" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="71"/>
+      <c r="C9" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="25">
+        <v>1.0435000000000001</v>
+      </c>
+      <c r="E9" s="26">
+        <v>5.2175000000000013E-2</v>
+      </c>
+      <c r="F9" s="27">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="G9" s="25">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H9" s="28">
         <v>0.7</v>
       </c>
-      <c r="I9" s="28" t="n">
+      <c r="I9" s="28">
         <v>159.25</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="29">
         <v>11.65</v>
       </c>
-      <c r="K9" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="28" t="n">
+      <c r="K9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="28">
         <v>0.05</v>
       </c>
-      <c r="O9" s="29" t="n">
+      <c r="O9" s="29">
         <v>0.45</v>
       </c>
-      <c r="P9" s="2" t="n"/>
+      <c r="P9" s="2"/>
     </row>
-    <row r="10" ht="15.6" customHeight="1">
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>NRM</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
+    <row r="10" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="71"/>
+      <c r="C10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="25">
         <v>2.214285714285714</v>
       </c>
-      <c r="E10" s="26" t="n">
-        <v>0.3163265306122449</v>
-      </c>
-      <c r="F10" s="27" t="n">
+      <c r="E10" s="26">
+        <v>0.31632653061224492</v>
+      </c>
+      <c r="F10" s="27">
         <v>0.2857142857142857</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="25">
         <v>1</v>
       </c>
-      <c r="H10" s="28" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>536.2857142857143</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>2.857142857142857</v>
-      </c>
-      <c r="K10" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="28" t="n">
+      <c r="H10" s="28">
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="I10" s="28">
+        <v>536.28571428571433</v>
+      </c>
+      <c r="J10" s="29">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="28">
         <v>1.428571428571429</v>
       </c>
-      <c r="O10" s="29" t="n">
+      <c r="O10" s="29">
         <v>0.2857142857142857</v>
       </c>
-      <c r="P10" s="2" t="n"/>
+      <c r="P10" s="2"/>
     </row>
-    <row r="11" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="69" t="n"/>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>Mechanization</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="31" t="n">
+    <row r="11" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="72"/>
+      <c r="C11" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="31">
+        <v>0</v>
+      </c>
+      <c r="E11" s="32">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+      <c r="G11" s="31">
         <v>0.5</v>
       </c>
-      <c r="H11" s="34" t="n">
+      <c r="H11" s="34">
         <v>0.25</v>
       </c>
-      <c r="I11" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="34" t="n">
+      <c r="I11" s="34">
+        <v>0</v>
+      </c>
+      <c r="J11" s="35">
+        <v>0</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="34">
         <v>0.75</v>
       </c>
-      <c r="O11" s="35" t="n">
+      <c r="O11" s="35">
         <v>0.75</v>
       </c>
-      <c r="P11" s="2" t="n"/>
+      <c r="P11" s="2"/>
     </row>
-    <row r="12" ht="15.6" customHeight="1">
-      <c r="B12" s="71" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>FIAS</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="n">
-        <v>0.9018181818181819</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>0.08198347107438017</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="37" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="H12" s="40" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="I12" s="41" t="n">
+    <row r="12" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="37">
+        <v>0.90181818181818185</v>
+      </c>
+      <c r="E12" s="38">
+        <v>8.1983471074380171E-2</v>
+      </c>
+      <c r="F12" s="39">
+        <v>0</v>
+      </c>
+      <c r="G12" s="37">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="H12" s="40">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="I12" s="41">
         <v>8.545454545454545</v>
       </c>
-      <c r="J12" s="42" t="n">
-        <v>9.909090909090908</v>
-      </c>
-      <c r="K12" s="43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="n"/>
+      <c r="J12" s="42">
+        <v>9.9090909090909083</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="40">
+        <v>0</v>
+      </c>
+      <c r="O12" s="44">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2"/>
     </row>
-    <row r="13" ht="15.6" customHeight="1">
-      <c r="B13" s="68" t="n"/>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>GeYSI</t>
-        </is>
-      </c>
-      <c r="D13" s="45" t="n">
+    <row r="13" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="71"/>
+      <c r="C13" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="45">
         <v>0.6</v>
       </c>
-      <c r="E13" s="46" t="n">
-        <v>0.05454545454545454</v>
-      </c>
-      <c r="F13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="45" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="H13" s="48" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>173.8181818181818</v>
-      </c>
-      <c r="J13" s="29" t="n">
+      <c r="E13" s="46">
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="F13" s="47">
+        <v>0</v>
+      </c>
+      <c r="G13" s="45">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="H13" s="48">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="I13" s="28">
+        <v>173.81818181818181</v>
+      </c>
+      <c r="J13" s="29">
         <v>14.18181818181818</v>
       </c>
-      <c r="K13" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="48" t="n">
-        <v>0.2272727272727273</v>
-      </c>
-      <c r="O13" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="n"/>
+      <c r="K13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="48">
+        <v>0.22727272727272729</v>
+      </c>
+      <c r="O13" s="49">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2"/>
     </row>
-    <row r="14" ht="15.6" customHeight="1">
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>2.666</v>
-      </c>
-      <c r="E14" s="46" t="n">
-        <v>0.5332</v>
-      </c>
-      <c r="F14" s="47" t="n">
+    <row r="14" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="71"/>
+      <c r="C14" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="45">
+        <v>2.6659999999999999</v>
+      </c>
+      <c r="E14" s="46">
+        <v>0.53320000000000001</v>
+      </c>
+      <c r="F14" s="47">
         <v>0.2</v>
       </c>
-      <c r="G14" s="45" t="n">
+      <c r="G14" s="45">
         <v>0.2</v>
       </c>
-      <c r="H14" s="48" t="n">
+      <c r="H14" s="48">
         <v>0.4</v>
       </c>
-      <c r="I14" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="48" t="n">
+      <c r="I14" s="28">
+        <v>0</v>
+      </c>
+      <c r="J14" s="29">
+        <v>0</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="48">
         <v>0.5</v>
       </c>
-      <c r="O14" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="n"/>
+      <c r="O14" s="49">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2"/>
     </row>
-    <row r="15" ht="15.6" customHeight="1">
-      <c r="B15" s="68" t="n"/>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>Nutrition</t>
-        </is>
-      </c>
-      <c r="D15" s="45" t="n">
+    <row r="15" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="71"/>
+      <c r="C15" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="45">
         <v>3.125</v>
       </c>
-      <c r="E15" s="46" t="n">
+      <c r="E15" s="46">
         <v>0.78125</v>
       </c>
-      <c r="F15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="45" t="n">
+      <c r="F15" s="47">
+        <v>0</v>
+      </c>
+      <c r="G15" s="45">
         <v>0.5</v>
       </c>
-      <c r="H15" s="48" t="n">
+      <c r="H15" s="48">
         <v>2</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="28">
         <v>32.5</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="29">
         <v>3.75</v>
       </c>
-      <c r="K15" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="n"/>
+      <c r="K15" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="48">
+        <v>0</v>
+      </c>
+      <c r="O15" s="49">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2"/>
     </row>
-    <row r="16" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B16" s="72" t="n"/>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>VCMA</t>
-        </is>
-      </c>
-      <c r="D16" s="50" t="n">
+    <row r="16" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="75"/>
+      <c r="C16" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="50">
         <v>0.3</v>
       </c>
-      <c r="E16" s="51" t="n">
+      <c r="E16" s="51">
         <v>0.03</v>
       </c>
-      <c r="F16" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="50" t="n">
+      <c r="F16" s="52">
+        <v>0</v>
+      </c>
+      <c r="G16" s="50">
         <v>0.5</v>
       </c>
-      <c r="H16" s="53" t="n">
+      <c r="H16" s="53">
         <v>0.3</v>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I16" s="34">
         <v>100.7</v>
       </c>
-      <c r="J16" s="35" t="n">
+      <c r="J16" s="35">
         <v>8.1</v>
       </c>
-      <c r="K16" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="n"/>
+      <c r="K16" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="53">
+        <v>0</v>
+      </c>
+      <c r="O16" s="54">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2"/>
     </row>
-    <row r="17" customFormat="1" s="55">
-      <c r="B17" s="56" t="n"/>
-      <c r="C17" s="58" t="inlineStr">
-        <is>
-          <t>per Program Target (target/13)</t>
-        </is>
-      </c>
-      <c r="D17" s="76" t="n">
-        <v>2.045112781954887</v>
-      </c>
-      <c r="E17" s="76" t="n">
-        <v>0.01503759398496241</v>
-      </c>
-      <c r="F17" s="76" t="n">
-        <v>0.09774436090225563</v>
-      </c>
-      <c r="G17" s="76" t="n">
-        <v>1.12781954887218</v>
-      </c>
-      <c r="H17" s="76" t="n">
-        <v>0.4511278195488722</v>
-      </c>
-      <c r="I17" s="76" t="n">
-        <v>90.22556390977444</v>
-      </c>
-      <c r="J17" s="76" t="n">
-        <v>1.12781954887218</v>
-      </c>
-      <c r="K17" s="76" t="n">
-        <v>0.04511278195488722</v>
-      </c>
-      <c r="L17" s="76" t="n">
-        <v>0.000112781954887218</v>
-      </c>
-      <c r="M17" s="76" t="n">
-        <v>0.007518796992481203</v>
-      </c>
-      <c r="N17" s="77" t="n">
-        <v>0.1503759398496241</v>
-      </c>
-      <c r="O17" s="77" t="n">
-        <v>0.2255639097744361</v>
-      </c>
-      <c r="P17" s="57" t="n"/>
-      <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="57" t="n"/>
-      <c r="S17" s="57" t="n"/>
-      <c r="T17" s="57" t="n"/>
-      <c r="U17" s="57" t="n"/>
-      <c r="V17" s="57" t="n"/>
+    <row r="17" spans="2:22" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="56"/>
+      <c r="C17" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="59">
+        <v>2.0451127819548871</v>
+      </c>
+      <c r="E17" s="59">
+        <v>1.503759398496241E-2</v>
+      </c>
+      <c r="F17" s="59">
+        <v>9.7744360902255634E-2</v>
+      </c>
+      <c r="G17" s="59">
+        <v>1.1278195488721801</v>
+      </c>
+      <c r="H17" s="59">
+        <v>0.45112781954887221</v>
+      </c>
+      <c r="I17" s="59">
+        <v>90.225563909774436</v>
+      </c>
+      <c r="J17" s="59">
+        <v>1.1278195488721801</v>
+      </c>
+      <c r="K17" s="59">
+        <v>4.5112781954887222E-2</v>
+      </c>
+      <c r="L17" s="59">
+        <v>0.01</v>
+      </c>
+      <c r="M17" s="59">
+        <v>7.5187969924812E-3</v>
+      </c>
+      <c r="N17" s="60">
+        <v>0.15037593984962411</v>
+      </c>
+      <c r="O17" s="60">
+        <v>0.22556390977443611</v>
+      </c>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="57"/>
     </row>
-    <row r="18"/>
-    <row r="19" hidden="1">
-      <c r="C19" s="61" t="n"/>
+    <row r="19" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="61"/>
     </row>
-    <row r="20" hidden="1">
-      <c r="C20" s="62" t="n"/>
+    <row r="20" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="62"/>
     </row>
-    <row r="21" hidden="1">
-      <c r="C21" s="63" t="n"/>
+    <row r="21" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="63"/>
     </row>
-    <row r="22" hidden="1"/>
+    <row r="22" spans="2:22" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="C1:O1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="C1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="149">
@@ -2706,9 +2535,15 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="60"/>
+  <pageSetup paperSize="8" scale="60" orientation="landscape"/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="7" min="0" max="18" man="1"/>
+    <brk id="7" max="18" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99805B30-D4D9-448E-BC15-084043C31420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597B485C-EA40-451D-9EBE-73FED2C8726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$B$1:$Q$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$B$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -158,7 +158,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,19 +174,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -699,253 +687,248 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1358,800 +1341,763 @@
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:W22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B1:Q22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="38.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="4.44140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" style="66" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="6.21875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="6.21875" style="10" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="10" customWidth="1"/>
-    <col min="14" max="14" width="6.21875" style="10" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="10" customWidth="1"/>
-    <col min="16" max="16" width="6.21875" style="10" customWidth="1"/>
-    <col min="17" max="17" width="5.44140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="6.21875" style="3" customWidth="1"/>
-    <col min="19" max="23" width="8.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="6.21875" style="7" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="6.21875" style="7" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="6.21875" style="7" customWidth="1"/>
+    <col min="17" max="17" width="8.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="15" thickBot="1">
-      <c r="C1" s="78" t="s">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="78"/>
     </row>
-    <row r="2" spans="2:23" s="6" customFormat="1" ht="18">
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="82" t="s">
+    <row r="2" spans="2:17" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="83"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="85" t="s">
+      <c r="F2" s="80"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="85" t="s">
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="2:23" s="11" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="64" t="s">
+    <row r="3" spans="2:17" s="8" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="54" t="s">
+      <c r="J3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="53" t="s">
+      <c r="L3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="56" t="s">
+      <c r="N3" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="54" t="s">
+      <c r="O3" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
+      <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="2:23" ht="15.45" customHeight="1">
-      <c r="B4" s="75" t="s">
+    <row r="4" spans="2:17" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="62">
         <v>7</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="10">
         <v>3.1428571428571428</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>3.1357142857142857</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="12">
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="10">
         <v>0.14285714285714285</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="13">
         <v>0.14285714285714285</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="13">
         <v>9.7142857142857135</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="14">
         <v>26.285714285714285</v>
       </c>
-      <c r="L4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="16">
+      <c r="L4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="13">
         <v>0.14285714285714285</v>
       </c>
-      <c r="P4" s="17">
+      <c r="P4" s="14">
         <v>0</v>
       </c>
-      <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B5" s="76"/>
-      <c r="C5" s="18" t="s">
+    <row r="5" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="73"/>
+      <c r="C5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="63">
         <v>23</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="16">
         <v>2.2391304347826089</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="17">
         <v>2.2369565217391307</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="18">
         <v>0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="16">
         <v>1.0434782608695652</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="19">
         <v>1.2173913043478262</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="19">
         <v>4.6956521739130439</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="20">
         <v>9.304347826086957</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="16">
         <f>'[1]PR 8'!$G$4</f>
         <v>0.65217391304347827</v>
       </c>
-      <c r="M5" s="22">
-        <f>'[1]PR 9'!$G$4</f>
-        <v>6.521739130434782E-4</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="O5" s="22">
+      <c r="M5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="19">
         <v>0.34782608695652173</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="20">
         <v>0.21739130434782608</v>
       </c>
-      <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B6" s="76"/>
-      <c r="C6" s="18" t="s">
+    <row r="6" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="73"/>
+      <c r="C6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="66">
+      <c r="D6" s="63">
         <v>4</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="16">
         <v>1.25</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="17">
         <v>1.25</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="18">
         <v>0</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="16">
         <v>6.5</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="19">
         <v>4.75</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="19">
         <v>1.25</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="20">
         <v>28.25</v>
       </c>
-      <c r="L6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="22">
-        <f>'[1]PR 10'!$G$5</f>
+      <c r="L6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="19">
         <v>0.25</v>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="19">
         <v>0</v>
       </c>
-      <c r="P6" s="23">
+      <c r="P6" s="20">
         <v>0</v>
       </c>
-      <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="77"/>
-      <c r="C7" s="24" t="s">
+    <row r="7" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="74"/>
+      <c r="C7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="64">
         <v>15</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="22">
         <v>1.0266666666666666</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="23">
         <v>1.0266666666666666</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="24">
         <v>0</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="22">
         <v>0.33333333333333331</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="25">
         <v>0.46666666666666667</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="25">
         <v>149.80000000000001</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="26">
         <v>20.6</v>
       </c>
-      <c r="L7" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="O7" s="28">
+      <c r="L7" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="25">
         <v>1.1333333333333333</v>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="26">
         <v>0.13333333333333333</v>
       </c>
-      <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B8" s="75" t="s">
+    <row r="8" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="62">
         <v>12</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>3.4541666666666671</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>3.4541666666666671</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="13">
         <v>0.75</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="13">
         <v>8.5</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="14">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L8" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="O8" s="16">
+      <c r="L8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="13">
         <v>0.5</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="14">
         <v>0.16666666666666666</v>
       </c>
-      <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B9" s="76"/>
-      <c r="C9" s="18" t="s">
+    <row r="9" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="73"/>
+      <c r="C9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="63">
         <v>20</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="16">
         <v>1.0435000000000001</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="17">
         <v>1.0435000000000001</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="18">
         <v>4.1499999999999995E-2</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="19">
         <v>0.7</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="19">
         <v>159.25</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="20">
         <v>11.65</v>
       </c>
-      <c r="L9" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="22">
+      <c r="L9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="19">
         <v>0.05</v>
       </c>
-      <c r="P9" s="23">
+      <c r="P9" s="20">
         <v>0.45</v>
       </c>
-      <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B10" s="76"/>
-      <c r="C10" s="18" t="s">
+    <row r="10" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="73"/>
+      <c r="C10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="63">
         <v>7</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="16">
         <v>2.2142857142857144</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="17">
         <v>2.2142857142857144</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="18">
         <v>0.2857142857142857</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="16">
         <v>1</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="19">
         <v>0.42857142857142855</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="19">
         <v>536.28571428571433</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="20">
         <v>2.8571428571428572</v>
       </c>
-      <c r="L10" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="22">
+      <c r="L10" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="19">
         <v>1.4285714285714286</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="20">
         <v>0.2857142857142857</v>
       </c>
-      <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="77"/>
-      <c r="C11" s="24" t="s">
+    <row r="11" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="74"/>
+      <c r="C11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="67">
+      <c r="D11" s="64">
         <v>4</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="22">
         <v>0</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="23">
         <v>0</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="24">
         <v>0</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="22">
         <v>0.5</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="25">
         <v>0.25</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="25">
         <v>0</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="26">
         <v>0</v>
       </c>
-      <c r="L11" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="28">
+      <c r="L11" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="25">
         <v>0.75</v>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="26">
         <v>0.75</v>
       </c>
-      <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B12" s="73" t="s">
+    <row r="12" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="68">
+      <c r="D12" s="65">
         <v>11</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="27">
         <v>0.90181818181818185</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="28">
         <v>0.90181818181818185</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="29">
         <v>0</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="27">
         <v>0.45454545454545453</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="30">
         <v>0.45454545454545453</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="31">
         <v>8.545454545454545</v>
       </c>
-      <c r="K12" s="35">
+      <c r="K12" s="32">
         <v>9.9090909090909083</v>
       </c>
-      <c r="L12" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="33">
+      <c r="L12" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="30">
         <v>0</v>
       </c>
-      <c r="P12" s="37">
+      <c r="P12" s="34">
         <v>0</v>
       </c>
-      <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B13" s="73"/>
-      <c r="C13" s="18" t="s">
+    <row r="13" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="70"/>
+      <c r="C13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="63">
         <v>11</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="35">
         <v>0.6</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="36">
         <v>0.6</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="37">
         <v>0</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="35">
         <v>0.36363636363636365</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="38">
         <v>0.27272727272727271</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="19">
         <v>173.81818181818181</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="20">
         <v>14.181818181818182</v>
       </c>
-      <c r="L13" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="41">
+      <c r="L13" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="38">
         <v>0.22727272727272727</v>
       </c>
-      <c r="P13" s="42">
+      <c r="P13" s="39">
         <v>0</v>
       </c>
-      <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B14" s="73"/>
-      <c r="C14" s="18" t="s">
+    <row r="14" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="70"/>
+      <c r="C14" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="63">
         <v>5</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="35">
         <v>2.6659999999999999</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="36">
         <v>2.6659999999999999</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="37">
         <v>0.2</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="35">
         <v>0.2</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="38">
         <v>0.4</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="19">
         <v>0</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="20">
         <v>0</v>
       </c>
-      <c r="L14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="41">
+      <c r="L14" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="38">
         <v>0.5</v>
       </c>
-      <c r="P14" s="42">
+      <c r="P14" s="39">
         <v>0</v>
       </c>
-      <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B15" s="73"/>
-      <c r="C15" s="18" t="s">
+    <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="70"/>
+      <c r="C15" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="63">
         <v>4</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="35">
         <v>3.125</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="36">
         <v>3.125</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="37">
         <v>0</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="35">
         <v>0.5</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="38">
         <v>2</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="19">
         <v>32.5</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="20">
         <v>3.75</v>
       </c>
-      <c r="L15" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="41">
+      <c r="L15" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="38">
         <v>0</v>
       </c>
-      <c r="P15" s="42">
+      <c r="P15" s="39">
         <v>0</v>
       </c>
-      <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B16" s="74"/>
-      <c r="C16" s="24" t="s">
+    <row r="16" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="71"/>
+      <c r="C16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="67">
+      <c r="D16" s="64">
         <v>10</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="40">
         <v>0.3</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="41">
         <v>0.3</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="42">
         <v>0</v>
       </c>
-      <c r="H16" s="43">
+      <c r="H16" s="40">
         <v>0.5</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="43">
         <v>0.3</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="25">
         <v>100.7</v>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="26">
         <v>8.1</v>
       </c>
-      <c r="L16" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="46">
+      <c r="L16" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="43">
         <v>0</v>
       </c>
-      <c r="P16" s="47">
+      <c r="P16" s="44">
         <v>0</v>
       </c>
-      <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="2:23" s="48" customFormat="1">
+    <row r="17" spans="2:17" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="72">
+      <c r="D17" s="69">
         <v>133</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="55">
         <v>2.0451127819548871</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F17" s="55">
         <f>E17</f>
         <v>2.0451127819548871</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="55">
         <v>9.7744360902255634E-2</v>
       </c>
-      <c r="H17" s="58">
+      <c r="H17" s="55">
         <v>1.1278195488721805</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17" s="55">
         <v>0.45112781954887216</v>
       </c>
-      <c r="J17" s="58">
+      <c r="J17" s="55">
         <v>90.225563909774436</v>
       </c>
-      <c r="K17" s="58">
+      <c r="K17" s="55">
         <v>1.1278195488721805</v>
       </c>
-      <c r="L17" s="58">
-        <v>4.5112781954887216E-2</v>
-      </c>
-      <c r="M17" s="58">
-        <v>1.1278195488721805E-4</v>
-      </c>
-      <c r="N17" s="58">
-        <v>7.5187969924812026E-3</v>
-      </c>
-      <c r="O17" s="59">
+      <c r="L17" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="56">
         <v>0.15037593984962405</v>
       </c>
-      <c r="P17" s="59">
+      <c r="P17" s="56">
         <v>0.22556390977443608</v>
       </c>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
+      <c r="Q17" s="46"/>
     </row>
-    <row r="18" spans="2:23">
-      <c r="F18" s="62"/>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="2:23" hidden="1">
-      <c r="C19" s="50"/>
-      <c r="D19" s="70"/>
+    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="47"/>
+      <c r="D19" s="67"/>
     </row>
-    <row r="20" spans="2:23" hidden="1">
-      <c r="C20" s="51"/>
+    <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="48"/>
     </row>
-    <row r="21" spans="2:23" hidden="1">
-      <c r="C21" s="52"/>
-      <c r="D21" s="71"/>
+    <row r="21" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="49"/>
+      <c r="D21" s="68"/>
     </row>
-    <row r="22" spans="2:23" hidden="1"/>
+    <row r="22" spans="2:17" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B12:B16"/>
@@ -2175,6 +2121,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
+    <cfRule type="colorScale" priority="152">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="151">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="min"/>
@@ -2185,28 +2151,18 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="151">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="152">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="153">
       <colorScale>
         <cfvo type="min"/>
@@ -2217,16 +2173,6 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="154">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="155">
       <colorScale>
         <cfvo type="min"/>
@@ -2330,8 +2276,8 @@
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$L$17/2"/>
-        <cfvo type="formula" val="$L$17"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF00B050"/>
@@ -2342,27 +2288,27 @@
     <cfRule type="colorScale" priority="165">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$M$17"/>
+        <cfvo type="formula" val="0"/>
         <color rgb="FFF8696B"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="101">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
@@ -2408,41 +2354,11 @@
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
+        <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="min"/>
@@ -2463,20 +2379,50 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="109">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX($M$4:$M$16)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="109">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
@@ -2495,46 +2441,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:N16">
-    <cfRule type="colorScale" priority="95">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="97">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="98">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="99">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2545,8 +2451,58 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N16">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
@@ -2601,16 +2557,6 @@
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX($M$4:$M$16)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597B485C-EA40-451D-9EBE-73FED2C8726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527C5265-7532-46CD-BA88-A4DE5A2D887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>Annual rate of genetic gain, by crop (%)</t>
   </si>
   <si>
-    <t>GI</t>
-  </si>
-  <si>
     <t>Biotech</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>Seed System</t>
   </si>
   <si>
-    <t>RAFS</t>
-  </si>
-  <si>
     <t>Plant Health</t>
   </si>
   <si>
@@ -93,9 +87,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
     <t>per Program Target (target/13)</t>
   </si>
   <si>
@@ -147,7 +138,16 @@
     <t>Value Chain Markets and Agribusiness</t>
   </si>
   <si>
-    <t>FTE</t>
+    <t>Genetic Innovation</t>
+  </si>
+  <si>
+    <t>Resilient Agrifood Systems</t>
+  </si>
+  <si>
+    <t>Systems Transformation</t>
+  </si>
+  <si>
+    <t>FTE - Number of staff</t>
   </si>
 </sst>
 </file>
@@ -687,7 +687,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -858,9 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1346,7 +1343,7 @@
   <cols>
     <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="38.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="4.44140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" style="65" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="6.21875" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.21875" style="7" customWidth="1"/>
     <col min="11" max="11" width="8.6640625" style="7" customWidth="1"/>
@@ -1359,73 +1356,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="78"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="77"/>
     </row>
     <row r="2" spans="2:17" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="B2" s="57"/>
       <c r="C2" s="58"/>
       <c r="D2" s="60"/>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="80"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="82" t="s">
+      <c r="F2" s="79"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="82" t="s">
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="84"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="83"/>
       <c r="Q2" s="3"/>
     </row>
     <row r="3" spans="2:17" s="8" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="50" t="s">
         <v>34</v>
       </c>
       <c r="E3" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="I3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="J3" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="K3" s="52" t="s">
         <v>21</v>
-      </c>
-      <c r="I3" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="52" t="s">
-        <v>24</v>
       </c>
       <c r="L3" s="50" t="s">
         <v>4</v>
@@ -1434,24 +1431,24 @@
         <v>5</v>
       </c>
       <c r="N3" s="53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O3" s="51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P3" s="52" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="2:17" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="62">
+      <c r="D4" s="61">
         <v>7</v>
       </c>
       <c r="E4" s="10">
@@ -1476,13 +1473,13 @@
         <v>26.285714285714285</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O4" s="13">
         <v>0.14285714285714285</v>
@@ -1492,11 +1489,11 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="73"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="63">
+        <v>8</v>
+      </c>
+      <c r="D5" s="62">
         <v>23</v>
       </c>
       <c r="E5" s="16">
@@ -1525,10 +1522,10 @@
         <v>0.65217391304347827</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O5" s="19">
         <v>0.34782608695652173</v>
@@ -1538,11 +1535,11 @@
       </c>
     </row>
     <row r="6" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="73"/>
+      <c r="B6" s="72"/>
       <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="63">
+        <v>9</v>
+      </c>
+      <c r="D6" s="62">
         <v>4</v>
       </c>
       <c r="E6" s="16">
@@ -1567,10 +1564,10 @@
         <v>28.25</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" s="19">
         <v>0.25</v>
@@ -1583,11 +1580,11 @@
       </c>
     </row>
     <row r="7" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="74"/>
+      <c r="B7" s="73"/>
       <c r="C7" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="64">
+        <v>10</v>
+      </c>
+      <c r="D7" s="63">
         <v>15</v>
       </c>
       <c r="E7" s="22">
@@ -1612,13 +1609,13 @@
         <v>20.6</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" s="25">
         <v>1.1333333333333333</v>
@@ -1628,13 +1625,13 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="72" t="s">
-        <v>12</v>
+      <c r="B8" s="71" t="s">
+        <v>32</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="62">
+        <v>11</v>
+      </c>
+      <c r="D8" s="61">
         <v>12</v>
       </c>
       <c r="E8" s="10">
@@ -1659,13 +1656,13 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O8" s="13">
         <v>0.5</v>
@@ -1675,11 +1672,11 @@
       </c>
     </row>
     <row r="9" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="73"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="63">
+        <v>12</v>
+      </c>
+      <c r="D9" s="62">
         <v>20</v>
       </c>
       <c r="E9" s="16">
@@ -1704,13 +1701,13 @@
         <v>11.65</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O9" s="19">
         <v>0.05</v>
@@ -1720,11 +1717,11 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="73"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="63">
+        <v>25</v>
+      </c>
+      <c r="D10" s="62">
         <v>7</v>
       </c>
       <c r="E10" s="16">
@@ -1749,13 +1746,13 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O10" s="19">
         <v>1.4285714285714286</v>
@@ -1765,11 +1762,11 @@
       </c>
     </row>
     <row r="11" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="74"/>
+      <c r="B11" s="73"/>
       <c r="C11" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="64">
+        <v>13</v>
+      </c>
+      <c r="D11" s="63">
         <v>4</v>
       </c>
       <c r="E11" s="22">
@@ -1794,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O11" s="25">
         <v>0.75</v>
@@ -1810,13 +1807,13 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="70" t="s">
-        <v>16</v>
+      <c r="B12" s="69" t="s">
+        <v>33</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="65">
+        <v>26</v>
+      </c>
+      <c r="D12" s="64">
         <v>11</v>
       </c>
       <c r="E12" s="27">
@@ -1841,13 +1838,13 @@
         <v>9.9090909090909083</v>
       </c>
       <c r="L12" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O12" s="30">
         <v>0</v>
@@ -1857,11 +1854,11 @@
       </c>
     </row>
     <row r="13" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="70"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="63">
+        <v>27</v>
+      </c>
+      <c r="D13" s="62">
         <v>11</v>
       </c>
       <c r="E13" s="35">
@@ -1886,13 +1883,13 @@
         <v>14.181818181818182</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O13" s="38">
         <v>0.22727272727272727</v>
@@ -1902,11 +1899,11 @@
       </c>
     </row>
     <row r="14" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="70"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="63">
+        <v>28</v>
+      </c>
+      <c r="D14" s="62">
         <v>5</v>
       </c>
       <c r="E14" s="35">
@@ -1931,13 +1928,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M14" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O14" s="38">
         <v>0.5</v>
@@ -1947,11 +1944,11 @@
       </c>
     </row>
     <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="70"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="63">
+        <v>29</v>
+      </c>
+      <c r="D15" s="62">
         <v>4</v>
       </c>
       <c r="E15" s="35">
@@ -1976,13 +1973,13 @@
         <v>3.75</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M15" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O15" s="38">
         <v>0</v>
@@ -1992,11 +1989,11 @@
       </c>
     </row>
     <row r="16" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="71"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="64">
+        <v>30</v>
+      </c>
+      <c r="D16" s="63">
         <v>10</v>
       </c>
       <c r="E16" s="40">
@@ -2021,13 +2018,13 @@
         <v>8.1</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M16" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O16" s="43">
         <v>0</v>
@@ -2039,17 +2036,16 @@
     <row r="17" spans="2:17" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="69">
+        <v>14</v>
+      </c>
+      <c r="D17" s="68">
         <v>133</v>
       </c>
       <c r="E17" s="55">
-        <v>2.0451127819548871</v>
+        <v>2</v>
       </c>
       <c r="F17" s="55">
-        <f>E17</f>
-        <v>2.0451127819548871</v>
+        <v>2</v>
       </c>
       <c r="G17" s="55">
         <v>9.7744360902255634E-2</v>
@@ -2067,13 +2063,13 @@
         <v>1.1278195488721805</v>
       </c>
       <c r="L17" s="55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M17" s="55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N17" s="55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O17" s="56">
         <v>0.15037593984962405</v>
@@ -2088,14 +2084,14 @@
     </row>
     <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" s="47"/>
-      <c r="D19" s="67"/>
+      <c r="D19" s="66"/>
     </row>
     <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="48"/>
     </row>
     <row r="21" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="49"/>
-      <c r="D21" s="68"/>
+      <c r="D21" s="67"/>
     </row>
     <row r="22" spans="2:17" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527C5265-7532-46CD-BA88-A4DE5A2D887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804B1A5B-9002-4EB6-B14E-EC3C07A18740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61134E1-F9C4-40AF-9F5C-C01B544E6BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAFACA5-B502-42B9-889B-BAACDAB60809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -242,7 +245,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -400,21 +403,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF00B050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -977,7 +965,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -994,34 +982,31 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1035,16 +1020,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1059,126 +1044,105 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1186,11 +1150,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1207,8 +1171,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1216,20 +1195,20 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1249,22 +1228,16 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1682,7 +1655,7 @@
   <cols>
     <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="6.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.21875" style="4" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" style="4" customWidth="1"/>
@@ -1695,296 +1668,296 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="34"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="85"/>
     </row>
-    <row r="2" spans="1:16" s="96" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="87" t="s">
+    <row r="2" spans="1:16" s="76" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="92"/>
+      <c r="B2" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="89" t="s">
+      <c r="C2" s="74"/>
+      <c r="D2" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="92" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="92" t="s">
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="95"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="75"/>
     </row>
     <row r="3" spans="1:16" s="5" customFormat="1" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="98"/>
+      <c r="A3" s="93"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="24" t="s">
         <v>22</v>
       </c>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:16" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="67">
         <v>7</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="30">
         <v>3.1428571428571428</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="31">
         <v>3.1357142857142857</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="32">
         <v>0.14285714285714285</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="30">
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="43">
         <v>0.14285714285714285</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="43">
         <v>9.7142857142857135</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4" s="44">
         <v>26.285714285714285</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="43">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O4" s="44">
         <v>0</v>
       </c>
-      <c r="L4" s="60">
+    </row>
+    <row r="5" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="80"/>
+      <c r="B5" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="68">
+        <v>23</v>
+      </c>
+      <c r="D5" s="33">
+        <v>2.2391304347826089</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2.2369565217391307</v>
+      </c>
+      <c r="F5" s="42">
         <v>0</v>
       </c>
-      <c r="M4" s="60">
-        <v>0</v>
-      </c>
-      <c r="N4" s="51">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="O4" s="52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
-      <c r="B5" s="73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="77">
-        <v>23</v>
-      </c>
-      <c r="D5" s="38">
-        <v>2.2391304347826089</v>
-      </c>
-      <c r="E5" s="9">
-        <v>2.2369565217391307</v>
-      </c>
-      <c r="F5" s="39">
-        <v>0</v>
-      </c>
-      <c r="G5" s="38">
+      <c r="G5" s="33">
         <v>1.0434782608695652</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <v>1.2173913043478262</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <v>4.6956521739130439</v>
       </c>
-      <c r="J5" s="53">
+      <c r="J5" s="45">
         <v>9.304347826086957</v>
       </c>
-      <c r="K5" s="38">
+      <c r="K5" s="33">
         <f>'[1]PR 8'!$G$4</f>
         <v>0.65217391304347827</v>
       </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="10">
+      <c r="L5" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="9">
         <v>0.34782608695652173</v>
       </c>
-      <c r="O5" s="53">
+      <c r="O5" s="45">
         <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="83"/>
-      <c r="B6" s="73" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="68">
         <v>4</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="33">
         <v>1.25</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>1.25</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="42">
         <v>0</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="33">
         <v>6.5</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>4.75</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>1.25</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="45">
         <v>28.25</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="9">
         <v>0</v>
       </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0</v>
-      </c>
-      <c r="O6" s="53">
+      <c r="O6" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="84"/>
-      <c r="B7" s="74" t="s">
+      <c r="A7" s="81"/>
+      <c r="B7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="69">
         <v>15</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="35">
         <v>1.0266666666666666</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>1.0266666666666666</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="42">
         <v>0</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="35">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.46666666666666667</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>149.80000000000001</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="46">
         <v>20.6</v>
       </c>
-      <c r="K7" s="40">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
+      <c r="K7" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="11">
         <v>1.1333333333333333</v>
       </c>
-      <c r="O7" s="54">
+      <c r="O7" s="46">
         <v>0.13333333333333333</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="82" t="s">
+    <row r="8" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="70">
         <v>12</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="36">
         <v>3.4541666666666671</v>
       </c>
       <c r="E8" s="6">
         <v>3.4541666666666671</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="37">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="36">
         <v>0.75</v>
       </c>
       <c r="H8" s="7">
@@ -1993,451 +1966,452 @@
       <c r="I8" s="7">
         <v>8.5</v>
       </c>
-      <c r="J8" s="55">
+      <c r="J8" s="47">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K8" s="42">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
+      <c r="K8" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="56" t="s">
+        <v>35</v>
       </c>
       <c r="N8" s="7">
         <v>0.5</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="47">
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="83"/>
-      <c r="B9" s="73" t="s">
+    <row r="9" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="80"/>
+      <c r="B9" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="68">
         <v>20</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="33">
         <v>1.0435000000000001</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>1.0435000000000001</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="34">
         <v>4.1499999999999995E-2</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="33">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <v>0.7</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>159.25</v>
       </c>
-      <c r="J9" s="53">
+      <c r="J9" s="45">
         <v>11.65</v>
       </c>
-      <c r="K9" s="38">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10">
+      <c r="K9" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="9">
         <v>0.05</v>
       </c>
-      <c r="O9" s="53">
+      <c r="O9" s="45">
         <v>0.45</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="83"/>
-      <c r="B10" s="73" t="s">
+    <row r="10" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="80"/>
+      <c r="B10" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="68">
         <v>7</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="33">
         <v>2.2142857142857144</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>2.2142857142857144</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="34">
         <v>0.2857142857142857</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="33">
         <v>1</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>0.42857142857142855</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>536.28571428571433</v>
       </c>
-      <c r="J10" s="53">
+      <c r="J10" s="45">
         <v>2.8571428571428572</v>
       </c>
-      <c r="K10" s="38">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8">
-        <v>0</v>
-      </c>
-      <c r="N10" s="10">
+      <c r="K10" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" s="9">
         <v>1.4285714285714286</v>
       </c>
-      <c r="O10" s="53">
+      <c r="O10" s="45">
         <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="84"/>
-      <c r="B11" s="74" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="69">
         <v>4</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="35">
         <v>0</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>0</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="42">
         <v>0</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="35">
         <v>0.5</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>0.25</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>0</v>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="46">
         <v>0</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="O11" s="46">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="71">
+        <v>11</v>
+      </c>
+      <c r="D12" s="38">
+        <v>0.90181818181818185</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0.90181818181818185</v>
+      </c>
+      <c r="F12" s="42">
         <v>0</v>
       </c>
-      <c r="L11" s="8">
+      <c r="G12" s="38">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="I12" s="14">
+        <v>8.545454545454545</v>
+      </c>
+      <c r="J12" s="48">
+        <v>9.9090909090909083</v>
+      </c>
+      <c r="K12" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="13">
         <v>0</v>
       </c>
-      <c r="M11" s="8">
+      <c r="O12" s="53">
         <v>0</v>
       </c>
-      <c r="N11" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="O11" s="54">
-        <v>0.75</v>
-      </c>
     </row>
-    <row r="12" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="85" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="80">
+    <row r="13" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="77"/>
+      <c r="B13" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="68">
         <v>11</v>
       </c>
-      <c r="D12" s="44">
-        <v>0.90181818181818185</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0.90181818181818185</v>
-      </c>
-      <c r="F12" s="45">
+      <c r="D13" s="39">
+        <v>0.6</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="F13" s="42">
         <v>0</v>
       </c>
-      <c r="G12" s="44">
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="H12" s="14">
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="I12" s="15">
-        <v>8.545454545454545</v>
-      </c>
-      <c r="J12" s="56">
-        <v>9.9090909090909083</v>
-      </c>
-      <c r="K12" s="61">
+      <c r="G13" s="39">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="I13" s="9">
+        <v>173.81818181818181</v>
+      </c>
+      <c r="J13" s="45">
+        <v>14.181818181818182</v>
+      </c>
+      <c r="K13" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="16">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="O13" s="54">
         <v>0</v>
       </c>
-      <c r="L12" s="8">
+    </row>
+    <row r="14" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="77"/>
+      <c r="B14" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="68">
+        <v>5</v>
+      </c>
+      <c r="D14" s="39">
+        <v>2.6659999999999999</v>
+      </c>
+      <c r="E14" s="15">
+        <v>2.6659999999999999</v>
+      </c>
+      <c r="F14" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="39">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="I14" s="9">
         <v>0</v>
       </c>
-      <c r="M12" s="8">
+      <c r="J14" s="45">
         <v>0</v>
       </c>
-      <c r="N12" s="14">
+      <c r="K14" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="O14" s="54">
         <v>0</v>
       </c>
-      <c r="O12" s="62">
+    </row>
+    <row r="15" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="77"/>
+      <c r="B15" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="68">
+        <v>4</v>
+      </c>
+      <c r="D15" s="39">
+        <v>3.125</v>
+      </c>
+      <c r="E15" s="15">
+        <v>3.125</v>
+      </c>
+      <c r="F15" s="42">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
-      <c r="B13" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="77">
-        <v>11</v>
-      </c>
-      <c r="D13" s="46">
-        <v>0.6</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="F13" s="47">
+      <c r="G15" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="16">
+        <v>2</v>
+      </c>
+      <c r="I15" s="9">
+        <v>32.5</v>
+      </c>
+      <c r="J15" s="45">
+        <v>3.75</v>
+      </c>
+      <c r="K15" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="16">
         <v>0</v>
       </c>
-      <c r="G13" s="46">
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="I13" s="10">
-        <v>173.81818181818181</v>
-      </c>
-      <c r="J13" s="53">
-        <v>14.181818181818182</v>
-      </c>
-      <c r="K13" s="38">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="17">
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="O13" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="85"/>
-      <c r="B14" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="77">
-        <v>5</v>
-      </c>
-      <c r="D14" s="46">
-        <v>2.6659999999999999</v>
-      </c>
-      <c r="E14" s="16">
-        <v>2.6659999999999999</v>
-      </c>
-      <c r="F14" s="47">
-        <v>0.2</v>
-      </c>
-      <c r="G14" s="46">
-        <v>0.2</v>
-      </c>
-      <c r="H14" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="I14" s="10">
-        <v>0</v>
-      </c>
-      <c r="J14" s="53">
-        <v>0</v>
-      </c>
-      <c r="K14" s="38">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8">
-        <v>0</v>
-      </c>
-      <c r="N14" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="O14" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
-      <c r="B15" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="77">
-        <v>4</v>
-      </c>
-      <c r="D15" s="46">
-        <v>3.125</v>
-      </c>
-      <c r="E15" s="16">
-        <v>3.125</v>
-      </c>
-      <c r="F15" s="47">
-        <v>0</v>
-      </c>
-      <c r="G15" s="46">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="17">
-        <v>2</v>
-      </c>
-      <c r="I15" s="10">
-        <v>32.5</v>
-      </c>
-      <c r="J15" s="53">
-        <v>3.75</v>
-      </c>
-      <c r="K15" s="38">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="63">
+      <c r="O15" s="54">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="86"/>
-      <c r="B16" s="75" t="s">
+      <c r="A16" s="78"/>
+      <c r="B16" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="81">
+      <c r="C16" s="72">
         <v>10</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="41">
         <v>0.3</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="42">
         <v>0.3</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="42">
         <v>0</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="41">
         <v>0.5</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="49">
         <v>0.3</v>
       </c>
-      <c r="I16" s="58">
+      <c r="I16" s="50">
         <v>100.7</v>
       </c>
-      <c r="J16" s="59">
+      <c r="J16" s="51">
         <v>8.1</v>
       </c>
-      <c r="K16" s="64">
+      <c r="K16" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="49">
         <v>0</v>
       </c>
-      <c r="L16" s="65">
+      <c r="O16" s="57">
         <v>0</v>
       </c>
-      <c r="M16" s="65">
+    </row>
+    <row r="17" spans="1:16" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="94"/>
+      <c r="B17" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="59">
+        <v>133</v>
+      </c>
+      <c r="D17" s="60">
+        <v>2</v>
+      </c>
+      <c r="E17" s="60">
+        <v>2</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="60">
+        <v>1.1278195488721805</v>
+      </c>
+      <c r="H17" s="60">
+        <v>0.45112781954887216</v>
+      </c>
+      <c r="I17" s="60">
+        <v>90.225563909774436</v>
+      </c>
+      <c r="J17" s="60">
+        <v>1.1278195488721805</v>
+      </c>
+      <c r="K17" s="60">
+        <v>0.01</v>
+      </c>
+      <c r="L17" s="60">
         <v>0</v>
       </c>
-      <c r="N16" s="57">
+      <c r="M17" s="60">
         <v>0</v>
       </c>
-      <c r="O16" s="66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="100"/>
-      <c r="B17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="68">
-        <v>133</v>
-      </c>
-      <c r="D17" s="69">
-        <v>2</v>
-      </c>
-      <c r="E17" s="69">
-        <v>2</v>
-      </c>
-      <c r="F17" s="69">
-        <v>9.7744360902255634E-2</v>
-      </c>
-      <c r="G17" s="69">
-        <v>1.1278195488721805</v>
-      </c>
-      <c r="H17" s="69">
-        <v>0.45112781954887216</v>
-      </c>
-      <c r="I17" s="69">
-        <v>90.225563909774436</v>
-      </c>
-      <c r="J17" s="69">
-        <v>1.1278195488721805</v>
-      </c>
-      <c r="K17" s="69">
-        <v>0</v>
-      </c>
-      <c r="L17" s="69">
-        <v>0</v>
-      </c>
-      <c r="M17" s="69">
-        <v>0</v>
-      </c>
-      <c r="N17" s="70">
+      <c r="N17" s="61">
         <v>0.15037593984962405</v>
       </c>
-      <c r="O17" s="71">
+      <c r="O17" s="62">
         <v>0.22556390977443608</v>
       </c>
-      <c r="P17" s="19"/>
+      <c r="P17" s="18"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="E18" s="27"/>
+      <c r="A18" s="95"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="20"/>
-      <c r="C19" s="29"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="28"/>
     </row>
     <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
+      <c r="B20" s="20"/>
     </row>
     <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="22"/>
-      <c r="C21" s="30"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="29"/>
     </row>
     <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
@@ -2446,10 +2420,9 @@
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="154">
+    <cfRule type="colorScale" priority="163">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -2461,7 +2434,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="155">
+    <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2471,7 +2444,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="156">
+    <cfRule type="colorScale" priority="165">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2481,7 +2454,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="157">
+    <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2492,8 +2465,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="158">
+  <conditionalFormatting sqref="F14 F4 F8:F10">
+    <cfRule type="colorScale" priority="167">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2503,7 +2476,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="159">
+    <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2513,7 +2486,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="160">
+    <cfRule type="colorScale" priority="169">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2525,7 +2498,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="161">
+    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2535,7 +2508,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="162">
+    <cfRule type="colorScale" priority="171">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2545,7 +2518,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="163">
+    <cfRule type="colorScale" priority="172">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2557,7 +2530,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H16">
-    <cfRule type="colorScale" priority="164">
+    <cfRule type="colorScale" priority="173">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$H$17/2"/>
@@ -2569,7 +2542,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="165">
+    <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2579,7 +2552,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="166">
+    <cfRule type="colorScale" priority="175">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2591,7 +2564,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="167">
+    <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2601,7 +2574,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="168">
+    <cfRule type="colorScale" priority="177">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2613,7 +2586,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="169">
+    <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="0.65"/>
@@ -2624,8 +2597,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N16">
-    <cfRule type="colorScale" priority="171">
+  <conditionalFormatting sqref="M4:M5 L4:L16">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M16">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M6">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$N$17/2"/>
@@ -2635,7 +2632,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="172">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2645,7 +2642,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="173">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2656,8 +2653,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N16">
+    <cfRule type="colorScale" priority="180">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$N$17/2"/>
+        <cfvo type="formula" val="$N$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="181">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="182">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="O4:O16">
-    <cfRule type="colorScale" priority="174">
+    <cfRule type="colorScale" priority="183">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$O$17/2"/>
@@ -2667,7 +2696,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="175">
+    <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2677,7 +2706,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="176">
+    <cfRule type="colorScale" priority="185">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2687,7 +2716,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="177">
+    <cfRule type="colorScale" priority="186">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2697,7 +2726,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="178">
+    <cfRule type="colorScale" priority="187">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2708,36 +2737,76 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L16">
+  <conditionalFormatting sqref="F15:F16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$E$17/2"/>
+        <cfvo type="formula" val="$E$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F13">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$E$17/2"/>
+        <cfvo type="formula" val="$E$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="0.65"/>
-        <cfvo type="formula" val="0.65"/>
-        <color rgb="FFFF0000"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M5 M7:M16">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="0.65"/>
-        <cfvo type="formula" val="0.65"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M6">
+  <conditionalFormatting sqref="F5:F7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$N$17/2"/>
-        <cfvo type="formula" val="$N$17"/>
+        <cfvo type="formula" val="$E$17/2"/>
+        <cfvo type="formula" val="$E$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAFACA5-B502-42B9-889B-BAACDAB60809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93F7807-C99F-4136-9D00-5525322A602E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -960,12 +960,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1050,31 +1049,19 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1241,10 +1228,9 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1668,51 +1654,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="85"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="81"/>
     </row>
-    <row r="2" spans="1:16" s="76" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="92"/>
-      <c r="B2" s="73" t="s">
+    <row r="2" spans="1:16" s="72" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="88"/>
+      <c r="B2" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="86" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="89" t="s">
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="75"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="71"/>
     </row>
     <row r="3" spans="1:16" s="5" customFormat="1" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="93"/>
+      <c r="A3" s="89"/>
       <c r="B3" s="3"/>
       <c r="C3" s="22" t="s">
         <v>32</v>
@@ -1756,13 +1742,13 @@
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="67">
+      <c r="C4" s="63">
         <v>7</v>
       </c>
       <c r="D4" s="30">
@@ -1771,55 +1757,55 @@
       <c r="E4" s="31">
         <v>3.1357142857142857</v>
       </c>
-      <c r="F4" s="32">
-        <v>0.14285714285714285</v>
+      <c r="F4" s="48" t="s">
+        <v>35</v>
       </c>
       <c r="G4" s="30">
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="39">
         <v>0.14285714285714285</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="39">
         <v>9.7142857142857135</v>
       </c>
-      <c r="J4" s="44">
+      <c r="J4" s="40">
         <v>26.285714285714285</v>
       </c>
       <c r="K4" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="43">
+      <c r="L4" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="39">
         <v>0.14285714285714285</v>
       </c>
-      <c r="O4" s="44">
+      <c r="O4" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="80"/>
-      <c r="B5" s="64" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="64">
         <v>23</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="32">
         <v>2.2391304347826089</v>
       </c>
       <c r="E5" s="8">
         <v>2.2369565217391307</v>
       </c>
-      <c r="F5" s="42">
-        <v>0</v>
-      </c>
-      <c r="G5" s="33">
+      <c r="F5" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="32">
         <v>1.0434782608695652</v>
       </c>
       <c r="H5" s="9">
@@ -1828,44 +1814,44 @@
       <c r="I5" s="9">
         <v>4.6956521739130439</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="41">
         <v>9.304347826086957</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="32">
         <f>'[1]PR 8'!$G$4</f>
         <v>0.65217391304347827</v>
       </c>
-      <c r="L5" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="52" t="s">
+      <c r="L5" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="48" t="s">
         <v>35</v>
       </c>
       <c r="N5" s="9">
         <v>0.34782608695652173</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="41">
         <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="80"/>
-      <c r="B6" s="64" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="64">
         <v>4</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="32">
         <v>1.25</v>
       </c>
       <c r="E6" s="8">
         <v>1.25</v>
       </c>
-      <c r="F6" s="42">
-        <v>0</v>
-      </c>
-      <c r="G6" s="33">
+      <c r="F6" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="32">
         <v>6.5</v>
       </c>
       <c r="H6" s="9">
@@ -1874,13 +1860,13 @@
       <c r="I6" s="9">
         <v>1.25</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="41">
         <v>28.25</v>
       </c>
-      <c r="K6" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="52" t="s">
+      <c r="K6" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="48" t="s">
         <v>35</v>
       </c>
       <c r="M6" s="11" t="s">
@@ -1889,28 +1875,28 @@
       <c r="N6" s="9">
         <v>0</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="81"/>
-      <c r="B7" s="65" t="s">
+      <c r="A7" s="77"/>
+      <c r="B7" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="65">
         <v>15</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="33">
         <v>1.0266666666666666</v>
       </c>
       <c r="E7" s="10">
         <v>1.0266666666666666</v>
       </c>
-      <c r="F7" s="42">
-        <v>0</v>
-      </c>
-      <c r="G7" s="35">
+      <c r="F7" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="33">
         <v>0.33333333333333331</v>
       </c>
       <c r="H7" s="11">
@@ -1919,45 +1905,45 @@
       <c r="I7" s="11">
         <v>149.80000000000001</v>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="42">
         <v>20.6</v>
       </c>
-      <c r="K7" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="56" t="s">
+      <c r="K7" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N7" s="11">
         <v>1.1333333333333333</v>
       </c>
-      <c r="O7" s="46">
+      <c r="O7" s="42">
         <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="66">
         <v>12</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="34">
         <v>3.4541666666666671</v>
       </c>
       <c r="E8" s="6">
         <v>3.4541666666666671</v>
       </c>
-      <c r="F8" s="37">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="G8" s="36">
+      <c r="F8" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="34">
         <v>0.75</v>
       </c>
       <c r="H8" s="7">
@@ -1966,43 +1952,43 @@
       <c r="I8" s="7">
         <v>8.5</v>
       </c>
-      <c r="J8" s="47">
+      <c r="J8" s="43">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K8" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="56" t="s">
+      <c r="K8" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N8" s="7">
         <v>0.5</v>
       </c>
-      <c r="O8" s="47">
+      <c r="O8" s="43">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="80"/>
-      <c r="B9" s="64" t="s">
+      <c r="A9" s="76"/>
+      <c r="B9" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="68">
+      <c r="C9" s="64">
         <v>20</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <v>1.0435000000000001</v>
       </c>
       <c r="E9" s="8">
         <v>1.0435000000000001</v>
       </c>
-      <c r="F9" s="34">
-        <v>4.1499999999999995E-2</v>
-      </c>
-      <c r="G9" s="33">
+      <c r="F9" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="32">
         <v>1.1000000000000001</v>
       </c>
       <c r="H9" s="9">
@@ -2011,43 +1997,43 @@
       <c r="I9" s="9">
         <v>159.25</v>
       </c>
-      <c r="J9" s="45">
+      <c r="J9" s="41">
         <v>11.65</v>
       </c>
-      <c r="K9" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="56" t="s">
+      <c r="K9" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N9" s="9">
         <v>0.05</v>
       </c>
-      <c r="O9" s="45">
+      <c r="O9" s="41">
         <v>0.45</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="80"/>
-      <c r="B10" s="64" t="s">
+      <c r="A10" s="76"/>
+      <c r="B10" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="68">
+      <c r="C10" s="64">
         <v>7</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>2.2142857142857144</v>
       </c>
       <c r="E10" s="8">
         <v>2.2142857142857144</v>
       </c>
-      <c r="F10" s="34">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G10" s="33">
+      <c r="F10" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="32">
         <v>1</v>
       </c>
       <c r="H10" s="9">
@@ -2056,43 +2042,43 @@
       <c r="I10" s="9">
         <v>536.28571428571433</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="41">
         <v>2.8571428571428572</v>
       </c>
-      <c r="K10" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="56" t="s">
+      <c r="K10" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N10" s="9">
         <v>1.4285714285714286</v>
       </c>
-      <c r="O10" s="45">
+      <c r="O10" s="41">
         <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="81"/>
-      <c r="B11" s="65" t="s">
+      <c r="A11" s="77"/>
+      <c r="B11" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="69">
+      <c r="C11" s="65">
         <v>4</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="33">
         <v>0</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
-      <c r="F11" s="42">
-        <v>0</v>
-      </c>
-      <c r="G11" s="35">
+      <c r="F11" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="33">
         <v>0.5</v>
       </c>
       <c r="H11" s="11">
@@ -2101,45 +2087,45 @@
       <c r="I11" s="11">
         <v>0</v>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="42">
         <v>0</v>
       </c>
-      <c r="K11" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="56" t="s">
+      <c r="K11" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N11" s="11">
         <v>0.75</v>
       </c>
-      <c r="O11" s="46">
+      <c r="O11" s="42">
         <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="71">
+      <c r="C12" s="67">
         <v>11</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="35">
         <v>0.90181818181818185</v>
       </c>
       <c r="E12" s="12">
         <v>0.90181818181818185</v>
       </c>
-      <c r="F12" s="42">
-        <v>0</v>
-      </c>
-      <c r="G12" s="38">
+      <c r="F12" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="35">
         <v>0.45454545454545453</v>
       </c>
       <c r="H12" s="13">
@@ -2148,43 +2134,43 @@
       <c r="I12" s="14">
         <v>8.545454545454545</v>
       </c>
-      <c r="J12" s="48">
+      <c r="J12" s="44">
         <v>9.9090909090909083</v>
       </c>
-      <c r="K12" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="56" t="s">
+      <c r="K12" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N12" s="13">
         <v>0</v>
       </c>
-      <c r="O12" s="53">
+      <c r="O12" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="77"/>
-      <c r="B13" s="64" t="s">
+      <c r="A13" s="73"/>
+      <c r="B13" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="68">
+      <c r="C13" s="64">
         <v>11</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="36">
         <v>0.6</v>
       </c>
       <c r="E13" s="15">
         <v>0.6</v>
       </c>
-      <c r="F13" s="42">
-        <v>0</v>
-      </c>
-      <c r="G13" s="39">
+      <c r="F13" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="36">
         <v>0.36363636363636365</v>
       </c>
       <c r="H13" s="16">
@@ -2193,43 +2179,43 @@
       <c r="I13" s="9">
         <v>173.81818181818181</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="41">
         <v>14.181818181818182</v>
       </c>
-      <c r="K13" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="56" t="s">
+      <c r="K13" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N13" s="16">
         <v>0.22727272727272727</v>
       </c>
-      <c r="O13" s="54">
+      <c r="O13" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="77"/>
-      <c r="B14" s="64" t="s">
+      <c r="A14" s="73"/>
+      <c r="B14" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="68">
+      <c r="C14" s="64">
         <v>5</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="36">
         <v>2.6659999999999999</v>
       </c>
       <c r="E14" s="15">
         <v>2.6659999999999999</v>
       </c>
-      <c r="F14" s="40">
-        <v>0.2</v>
-      </c>
-      <c r="G14" s="39">
+      <c r="F14" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="36">
         <v>0.2</v>
       </c>
       <c r="H14" s="16">
@@ -2238,43 +2224,43 @@
       <c r="I14" s="9">
         <v>0</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="41">
         <v>0</v>
       </c>
-      <c r="K14" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="56" t="s">
+      <c r="K14" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N14" s="16">
         <v>0.5</v>
       </c>
-      <c r="O14" s="54">
+      <c r="O14" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="77"/>
-      <c r="B15" s="64" t="s">
+      <c r="A15" s="73"/>
+      <c r="B15" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="68">
+      <c r="C15" s="64">
         <v>4</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="36">
         <v>3.125</v>
       </c>
       <c r="E15" s="15">
         <v>3.125</v>
       </c>
-      <c r="F15" s="42">
-        <v>0</v>
-      </c>
-      <c r="G15" s="39">
+      <c r="F15" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="36">
         <v>0.5</v>
       </c>
       <c r="H15" s="16">
@@ -2283,118 +2269,118 @@
       <c r="I15" s="9">
         <v>32.5</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="41">
         <v>3.75</v>
       </c>
-      <c r="K15" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="56" t="s">
+      <c r="K15" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="52" t="s">
         <v>35</v>
       </c>
       <c r="N15" s="16">
         <v>0</v>
       </c>
-      <c r="O15" s="54">
+      <c r="O15" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="78"/>
-      <c r="B16" s="66" t="s">
+      <c r="A16" s="74"/>
+      <c r="B16" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="68">
         <v>10</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="37">
         <v>0.3</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="38">
         <v>0.3</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="45">
+        <v>0.3</v>
+      </c>
+      <c r="I16" s="46">
+        <v>100.7</v>
+      </c>
+      <c r="J16" s="47">
+        <v>8.1</v>
+      </c>
+      <c r="K16" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="45">
         <v>0</v>
       </c>
-      <c r="G16" s="41">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="I16" s="50">
-        <v>100.7</v>
-      </c>
-      <c r="J16" s="51">
-        <v>8.1</v>
-      </c>
-      <c r="K16" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="N16" s="49">
-        <v>0</v>
-      </c>
-      <c r="O16" s="57">
+      <c r="O16" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="94"/>
-      <c r="B17" s="58" t="s">
+      <c r="A17" s="90"/>
+      <c r="B17" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="55">
         <v>133</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="56">
         <v>2</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="56">
         <v>2</v>
       </c>
-      <c r="F17" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="60">
+      <c r="F17" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="56">
         <v>1.1278195488721805</v>
       </c>
-      <c r="H17" s="60">
+      <c r="H17" s="56">
         <v>0.45112781954887216</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="56">
         <v>90.225563909774436</v>
       </c>
-      <c r="J17" s="60">
+      <c r="J17" s="56">
         <v>1.1278195488721805</v>
       </c>
-      <c r="K17" s="60">
+      <c r="K17" s="56">
         <v>0.01</v>
       </c>
-      <c r="L17" s="60">
-        <v>0</v>
-      </c>
-      <c r="M17" s="60">
-        <v>0</v>
-      </c>
-      <c r="N17" s="61">
+      <c r="L17" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="57">
         <v>0.15037593984962405</v>
       </c>
-      <c r="O17" s="62">
+      <c r="O17" s="58">
         <v>0.22556390977443608</v>
       </c>
       <c r="P17" s="18"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="95"/>
+      <c r="A18" s="91"/>
       <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
@@ -2422,7 +2408,7 @@
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="163">
+    <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -2434,7 +2420,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="164">
+    <cfRule type="colorScale" priority="165">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2442,16 +2428,6 @@
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="165">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="166">
@@ -2464,29 +2440,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F4 F8:F10">
     <cfRule type="colorScale" priority="167">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$F$17/2"/>
-        <cfvo type="formula" val="$F$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="168">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="169">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2498,7 +2452,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="170">
+    <cfRule type="colorScale" priority="171">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2506,16 +2460,6 @@
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="171">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="172">
@@ -2528,9 +2472,19 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="173">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H16">
-    <cfRule type="colorScale" priority="173">
+    <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$H$17/2"/>
@@ -2542,7 +2496,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="174">
+    <cfRule type="colorScale" priority="175">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2552,7 +2506,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="175">
+    <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2564,7 +2518,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="176">
+    <cfRule type="colorScale" priority="177">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2574,7 +2528,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="177">
+    <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2586,7 +2540,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="178">
+    <cfRule type="colorScale" priority="179">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="0.65"/>
@@ -2598,6 +2552,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M5 L4:L16">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M16">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2609,20 +2575,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M16">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="0.65"/>
-        <cfvo type="formula" val="0.65"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M6">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$N$17/2"/>
@@ -2630,16 +2584,6 @@
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -2652,9 +2596,19 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N16">
-    <cfRule type="colorScale" priority="180">
+    <cfRule type="colorScale" priority="181">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$N$17/2"/>
@@ -2662,16 +2616,6 @@
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="181">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="182">
@@ -2684,9 +2628,19 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="183">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O16">
-    <cfRule type="colorScale" priority="183">
+    <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$O$17/2"/>
@@ -2694,16 +2648,6 @@
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="184">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="185">
@@ -2728,6 +2672,16 @@
     </cfRule>
     <cfRule type="colorScale" priority="187">
       <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="188">
+      <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
         <cfvo type="max"/>
@@ -2737,99 +2691,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F16">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$E$17/2"/>
-        <cfvo type="formula" val="$E$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11:F13">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$E$17/2"/>
-        <cfvo type="formula" val="$E$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F7">
+  <conditionalFormatting sqref="F4:F16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$E$17/2"/>
-        <cfvo type="formula" val="$E$17"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93F7807-C99F-4136-9D00-5525322A602E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437B531B-1D2A-4026-A997-E118B27A1EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
@@ -975,39 +975,6 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1043,91 +1010,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1170,6 +1056,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1221,11 +1113,119 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1641,7 +1641,7 @@
   <cols>
     <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="6.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.21875" style="4" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" style="4" customWidth="1"/>
@@ -1654,745 +1654,745 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="81"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="45"/>
     </row>
-    <row r="2" spans="1:16" s="72" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="88"/>
-      <c r="B2" s="69" t="s">
+    <row r="2" spans="1:16" s="34" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="52"/>
+      <c r="B2" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="82" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="85" t="s">
+      <c r="E2" s="47"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="85" t="s">
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="71"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="33"/>
     </row>
     <row r="3" spans="1:16" s="5" customFormat="1" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="89"/>
+      <c r="A3" s="53"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="M3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="N3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="13" t="s">
         <v>22</v>
       </c>
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="25">
         <v>7</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="54">
         <v>3.1428571428571428</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="55">
         <v>3.1357142857142857</v>
       </c>
-      <c r="F4" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="30">
+      <c r="F4" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="54">
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="39">
+      <c r="H4" s="57">
         <v>0.14285714285714285</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="57">
         <v>9.7142857142857135</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="58">
         <v>26.285714285714285</v>
       </c>
-      <c r="K4" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="39">
+      <c r="K4" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="57">
         <v>0.14285714285714285</v>
       </c>
-      <c r="O4" s="40">
+      <c r="O4" s="58">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
-      <c r="B5" s="60" t="s">
+      <c r="A5" s="40"/>
+      <c r="B5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="64">
+      <c r="C5" s="26">
         <v>23</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="59">
         <v>2.2391304347826089</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="60">
         <v>2.2369565217391307</v>
       </c>
-      <c r="F5" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="32">
+      <c r="F5" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="59">
         <v>1.0434782608695652</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="61">
         <v>1.2173913043478262</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="61">
         <v>4.6956521739130439</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="62">
         <v>9.304347826086957</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="59">
         <f>'[1]PR 8'!$G$4</f>
         <v>0.65217391304347827</v>
       </c>
-      <c r="L5" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="9">
+      <c r="L5" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="61">
         <v>0.34782608695652173</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="62">
         <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
-      <c r="B6" s="60" t="s">
+      <c r="A6" s="40"/>
+      <c r="B6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="64">
+      <c r="C6" s="26">
         <v>4</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="59">
         <v>1.25</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="60">
         <v>1.25</v>
       </c>
-      <c r="F6" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="32">
+      <c r="F6" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="59">
         <v>6.5</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="61">
         <v>4.75</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="61">
         <v>1.25</v>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="62">
         <v>28.25</v>
       </c>
-      <c r="K6" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" s="9">
+      <c r="K6" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="61">
         <v>0</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="62">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="77"/>
-      <c r="B7" s="61" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="65">
+      <c r="C7" s="27">
         <v>15</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="65">
         <v>1.0266666666666666</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="66">
         <v>1.0266666666666666</v>
       </c>
-      <c r="F7" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="33">
+      <c r="F7" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="65">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="64">
         <v>0.46666666666666667</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="64">
         <v>149.80000000000001</v>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="67">
         <v>20.6</v>
       </c>
-      <c r="K7" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="11">
+      <c r="K7" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="64">
         <v>1.1333333333333333</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="67">
         <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="28">
         <v>12</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="69">
         <v>3.4541666666666671</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="70">
         <v>3.4541666666666671</v>
       </c>
-      <c r="F8" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="34">
+      <c r="F8" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="69">
         <v>0.75</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="71">
         <v>0.75</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="71">
         <v>8.5</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="72">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K8" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="7">
+      <c r="K8" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="71">
         <v>0.5</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="72">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="76"/>
-      <c r="B9" s="60" t="s">
+      <c r="A9" s="40"/>
+      <c r="B9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="64">
+      <c r="C9" s="26">
         <v>20</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="59">
         <v>1.0435000000000001</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="60">
         <v>1.0435000000000001</v>
       </c>
-      <c r="F9" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="32">
+      <c r="F9" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="59">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="61">
         <v>0.7</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="61">
         <v>159.25</v>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="62">
         <v>11.65</v>
       </c>
-      <c r="K9" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="9">
+      <c r="K9" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="61">
         <v>0.05</v>
       </c>
-      <c r="O9" s="41">
+      <c r="O9" s="62">
         <v>0.45</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="76"/>
-      <c r="B10" s="60" t="s">
+      <c r="A10" s="40"/>
+      <c r="B10" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="64">
+      <c r="C10" s="26">
         <v>7</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="59">
         <v>2.2142857142857144</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="60">
         <v>2.2142857142857144</v>
       </c>
-      <c r="F10" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="32">
+      <c r="F10" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="59">
         <v>1</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="61">
         <v>0.42857142857142855</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="61">
         <v>536.28571428571433</v>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="62">
         <v>2.8571428571428572</v>
       </c>
-      <c r="K10" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="9">
+      <c r="K10" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" s="61">
         <v>1.4285714285714286</v>
       </c>
-      <c r="O10" s="41">
+      <c r="O10" s="62">
         <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="77"/>
-      <c r="B11" s="61" t="s">
+      <c r="A11" s="41"/>
+      <c r="B11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="27">
         <v>4</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="65">
         <v>0</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="66">
         <v>0</v>
       </c>
-      <c r="F11" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="33">
+      <c r="F11" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="65">
         <v>0.5</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="64">
         <v>0.25</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="64">
         <v>0</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="67">
         <v>0</v>
       </c>
-      <c r="K11" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="11">
+      <c r="K11" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" s="64">
         <v>0.75</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="67">
         <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="29">
         <v>11</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="73">
         <v>0.90181818181818185</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="74">
         <v>0.90181818181818185</v>
       </c>
-      <c r="F12" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="35">
+      <c r="F12" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="73">
         <v>0.45454545454545453</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="75">
         <v>0.45454545454545453</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="76">
         <v>8.545454545454545</v>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="77">
         <v>9.9090909090909083</v>
       </c>
-      <c r="K12" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="13">
+      <c r="K12" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="75">
         <v>0</v>
       </c>
-      <c r="O12" s="49">
+      <c r="O12" s="78">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="73"/>
-      <c r="B13" s="60" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="64">
+      <c r="C13" s="26">
         <v>11</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="79">
         <v>0.6</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="80">
         <v>0.6</v>
       </c>
-      <c r="F13" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="36">
+      <c r="F13" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="79">
         <v>0.36363636363636365</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="81">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="61">
         <v>173.81818181818181</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="62">
         <v>14.181818181818182</v>
       </c>
-      <c r="K13" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="16">
+      <c r="K13" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="81">
         <v>0.22727272727272727</v>
       </c>
-      <c r="O13" s="50">
+      <c r="O13" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="73"/>
-      <c r="B14" s="60" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="64">
+      <c r="C14" s="26">
         <v>5</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="79">
         <v>2.6659999999999999</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="80">
         <v>2.6659999999999999</v>
       </c>
-      <c r="F14" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="36">
+      <c r="F14" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="79">
         <v>0.2</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="81">
         <v>0.4</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="61">
         <v>0</v>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="62">
         <v>0</v>
       </c>
-      <c r="K14" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="16">
+      <c r="K14" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="81">
         <v>0.5</v>
       </c>
-      <c r="O14" s="50">
+      <c r="O14" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="73"/>
-      <c r="B15" s="60" t="s">
+      <c r="A15" s="37"/>
+      <c r="B15" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="64">
+      <c r="C15" s="26">
         <v>4</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="79">
         <v>3.125</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="80">
         <v>3.125</v>
       </c>
-      <c r="F15" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="36">
+      <c r="F15" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="79">
         <v>0.5</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="81">
         <v>2</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="61">
         <v>32.5</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="62">
         <v>3.75</v>
       </c>
-      <c r="K15" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" s="16">
+      <c r="K15" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="81">
         <v>0</v>
       </c>
-      <c r="O15" s="50">
+      <c r="O15" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="74"/>
-      <c r="B16" s="62" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="68">
+      <c r="C16" s="30">
         <v>10</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="83">
         <v>0.3</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="84">
         <v>0.3</v>
       </c>
-      <c r="F16" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="37">
+      <c r="F16" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="83">
         <v>0.5</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="85">
         <v>0.3</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="86">
         <v>100.7</v>
       </c>
-      <c r="J16" s="47">
+      <c r="J16" s="87">
         <v>8.1</v>
       </c>
-      <c r="K16" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="N16" s="45">
+      <c r="K16" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="85">
         <v>0</v>
       </c>
-      <c r="O16" s="53">
+      <c r="O16" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="90"/>
-      <c r="B17" s="54" t="s">
+    <row r="17" spans="1:16" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="35"/>
+      <c r="B17" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="20">
         <v>133</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="89">
         <v>2</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="89">
         <v>2</v>
       </c>
-      <c r="F17" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="56">
+      <c r="F17" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="89">
         <v>1.1278195488721805</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="89">
         <v>0.45112781954887216</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="89">
         <v>90.225563909774436</v>
       </c>
-      <c r="J17" s="56">
+      <c r="J17" s="89">
         <v>1.1278195488721805</v>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="89">
         <v>0.01</v>
       </c>
-      <c r="L17" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="57">
+      <c r="L17" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="90">
         <v>0.15037593984962405</v>
       </c>
-      <c r="O17" s="58">
+      <c r="O17" s="91">
         <v>0.22556390977443608</v>
       </c>
-      <c r="P17" s="18"/>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
-      <c r="E18" s="26"/>
+      <c r="A18" s="36"/>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="19"/>
-      <c r="C19" s="28"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="20"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="29"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="18"/>
     </row>
     <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2448,6 +2448,18 @@
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2563,18 +2575,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M16">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="0.65"/>
-        <cfvo type="formula" val="0.65"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M6">
     <cfRule type="colorScale" priority="11">
       <colorScale>
@@ -2604,6 +2604,18 @@
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M16">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2691,18 +2703,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="0.65"/>
-        <cfvo type="formula" val="0.65"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="60" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{390E8B1D-AD65-4E72-9311-9F292F9257FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C14F4389-C1CD-40AF-82AF-C8C0D9FA7CCC}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{390E8B1D-AD65-4E72-9311-9F292F9257FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64746FF5-2D82-47A4-A3FF-9FCE23C6A99B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$A$1:$O$17</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -138,10 +138,6 @@
     <t>Systems Transformation</t>
   </si>
   <si>
-    <t>FTE - Number
- of staff</t>
-  </si>
-  <si>
     <t>IITA Program</t>
   </si>
   <si>
@@ -152,6 +148,10 @@
   </si>
   <si>
     <t xml:space="preserve">per Program Target </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTE - Number of staff
+</t>
   </si>
 </sst>
 </file>
@@ -159,8 +159,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -705,21 +705,21 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -735,7 +735,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -756,180 +756,174 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -954,7 +948,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PR 1"/>
@@ -978,13 +971,55 @@
       <sheetName val="PR20"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="G3">
+            <v>3.1428571428571428</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="G3">
+            <v>0.44795918367346937</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="3">
+          <cell r="G3">
+            <v>0.14285714285714285</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="3">
+          <cell r="G3">
+            <v>0.14285714285714285</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="3">
+          <cell r="G3">
+            <v>0.14285714285714285</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5">
+        <row r="3">
+          <cell r="G3">
+            <v>9.7142857142857135</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="3">
+          <cell r="G3">
+            <v>26.285714285714285</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="7">
         <row r="4">
           <cell r="G4">
@@ -993,16 +1028,58 @@
         </row>
       </sheetData>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="G5">
+            <v>0.25</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="11">
+        <row r="3">
+          <cell r="G3">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12">
+        <row r="6">
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="14">
+        <row r="3">
+          <cell r="G3">
+            <v>0.14285714285714285</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="16">
+        <row r="4">
+          <cell r="G4">
+            <v>8.6956521739130432E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17">
+        <row r="4">
+          <cell r="G4">
+            <v>4.3478260869565216E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="18">
+        <row r="4">
+          <cell r="G4">
+            <v>8.6956521739130432E-2</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1330,76 +1407,76 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.81640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="5.90625" style="1" customWidth="1"/>
-    <col min="9" max="15" width="5.90625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="8.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.88671875" style="1" customWidth="1"/>
+    <col min="9" max="15" width="5.88671875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="8.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="62"/>
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="67"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="69"/>
     </row>
-    <row r="2" spans="1:16" s="21" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="44"/>
+    <row r="2" spans="1:16" s="21" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="76"/>
       <c r="B2" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="19"/>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="59" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="59" t="s">
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="61"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="75"/>
       <c r="P2" s="20"/>
     </row>
-    <row r="3" spans="1:16" s="5" customFormat="1" ht="118.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="44"/>
+    <row r="3" spans="1:16" s="5" customFormat="1" ht="108.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="76"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="57" t="s">
+      <c r="C3" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="28" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -1408,10 +1485,10 @@
       <c r="I3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="58" t="s">
+      <c r="J3" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="L3" s="12" t="s">
@@ -1423,665 +1500,665 @@
       <c r="N3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="58" t="s">
+      <c r="O3" s="29" t="s">
         <v>21</v>
       </c>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="46">
+      <c r="B4" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="23">
         <v>7</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="34">
         <v>3.1428571428571428</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="35">
         <v>3.1357142857142857</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="22">
+      <c r="F4" s="36">
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="24">
+      <c r="G4" s="34">
         <v>0.14285714285714285</v>
       </c>
-      <c r="I4" s="24">
+      <c r="H4" s="37">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I4" s="37">
         <v>9.7142857142857135</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="36">
         <v>26.285714285714285</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="24">
+      <c r="K4" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="37">
         <v>0.14285714285714285</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="65"/>
+    <row r="5" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="64"/>
       <c r="B5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="24">
         <v>23</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="22">
         <v>2.2391304347826089</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="38">
         <v>2.2369565217391307</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="F5" s="39">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
         <v>1.0434782608695652</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="26">
         <v>1.2173913043478262</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="26">
         <v>4.6956521739130439</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="39">
         <v>9.304347826086957</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="22">
         <f>'[1]PR 8'!$G$4</f>
         <v>2</v>
       </c>
-      <c r="L5" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5" s="28">
+      <c r="L5" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="26">
         <v>0.34782608695652173</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="39">
         <v>0.21739130434782608</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="65"/>
+    <row r="6" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="64"/>
       <c r="B6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="24">
         <v>4</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="22">
         <v>1.25</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="38">
         <v>1.25</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="F6" s="39">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22">
         <v>6.5</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="26">
         <v>4.75</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="26">
         <v>1.25</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="39">
         <v>28.25</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6" s="28">
-        <v>0</v>
-      </c>
-      <c r="O6" s="29">
+      <c r="K6" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="26">
+        <v>0</v>
+      </c>
+      <c r="O6" s="39">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67" t="s">
+    <row r="7" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="65"/>
+      <c r="B7" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="25">
         <v>15</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="40">
         <v>1.0266666666666666</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="41">
         <v>1.0266666666666666</v>
       </c>
-      <c r="F7" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="42">
+        <v>0</v>
+      </c>
+      <c r="G7" s="40">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="43">
         <v>0.46666666666666667</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="43">
         <v>149.80000000000001</v>
       </c>
-      <c r="J7" s="39">
+      <c r="J7" s="42">
         <v>20.6</v>
       </c>
-      <c r="K7" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" s="38">
+      <c r="K7" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="43">
         <v>1.1333333333333333</v>
       </c>
-      <c r="O7" s="39">
+      <c r="O7" s="42">
         <v>0.13333333333333333</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="23">
         <v>12</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="34">
         <v>3.4541666666666671</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="35">
         <v>3.4541666666666671</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="22">
+      <c r="F8" s="36">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G8" s="34">
         <v>0.75</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="37">
         <v>0.75</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="37">
         <v>8.5</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="36">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="24">
+      <c r="K8" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="37">
         <v>0.5</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="36">
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="65"/>
+    <row r="9" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="64"/>
       <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="24">
         <v>20</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="22">
         <v>1.0435000000000001</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="38">
         <v>1.0435000000000001</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="F9" s="39">
+        <v>4.1499999999999995E-2</v>
+      </c>
+      <c r="G9" s="22">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="26">
         <v>0.7</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="26">
         <v>159.25</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="39">
         <v>11.65</v>
       </c>
-      <c r="K9" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="K9" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="26">
         <v>0.05</v>
       </c>
-      <c r="O9" s="29">
+      <c r="O9" s="39">
         <v>0.45</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="65"/>
+    <row r="10" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="64"/>
       <c r="B10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="24">
         <v>7</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="22">
         <v>2.2142857142857144</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="38">
         <v>2.2142857142857144</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="26">
+      <c r="F10" s="39">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G10" s="22">
         <v>1</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="26">
         <v>0.42857142857142855</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="26">
         <v>536.28571428571433</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="39">
         <v>2.8571428571428572</v>
       </c>
-      <c r="K10" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10" s="28">
+      <c r="K10" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="26">
         <v>1.4285714285714286</v>
       </c>
-      <c r="O10" s="29">
+      <c r="O10" s="39">
         <v>0.2857142857142857</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67" t="s">
+    <row r="11" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="65"/>
+      <c r="B11" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="25">
         <v>4</v>
       </c>
-      <c r="D11" s="30">
-        <v>0</v>
-      </c>
-      <c r="E11" s="68">
-        <v>0</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="30">
+      <c r="D11" s="40">
+        <v>0</v>
+      </c>
+      <c r="E11" s="41">
+        <v>0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0</v>
+      </c>
+      <c r="G11" s="40">
         <v>0.5</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="43">
         <v>0.25</v>
       </c>
-      <c r="I11" s="38">
-        <v>0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>0</v>
-      </c>
-      <c r="K11" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" s="38">
+      <c r="I11" s="43">
+        <v>0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>0</v>
+      </c>
+      <c r="K11" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="43">
         <v>0.75</v>
       </c>
-      <c r="O11" s="39">
+      <c r="O11" s="42">
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="72" t="s">
+    <row r="12" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="23">
         <v>11</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="44">
         <v>0.90181818181818185</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="45">
         <v>0.90181818181818185</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="73">
+      <c r="F12" s="36">
+        <v>0</v>
+      </c>
+      <c r="G12" s="44">
         <v>0.45454545454545453</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="46">
         <v>0.45454545454545453</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="37">
         <v>8.545454545454545</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="36">
         <v>9.9090909090909083</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="75">
-        <v>0</v>
-      </c>
-      <c r="O12" s="76">
+      <c r="K12" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="46">
+        <v>0</v>
+      </c>
+      <c r="O12" s="47">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="77"/>
+    <row r="13" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="61"/>
       <c r="B13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="24">
         <v>11</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="48">
         <v>0.6</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="49">
         <v>0.6</v>
       </c>
-      <c r="F13" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="31">
+      <c r="F13" s="39">
+        <v>0</v>
+      </c>
+      <c r="G13" s="48">
         <v>0.36363636363636365</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="50">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="26">
         <v>173.81818181818181</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="39">
         <v>14.181818181818182</v>
       </c>
-      <c r="K13" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N13" s="33">
+      <c r="K13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="50">
         <v>0.22727272727272727</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="51">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="77"/>
+    <row r="14" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="61"/>
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="24">
         <v>5</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="48">
         <v>2.6659999999999999</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="49">
         <v>2.6659999999999999</v>
       </c>
-      <c r="F14" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="31">
+      <c r="F14" s="39">
         <v>0.2</v>
       </c>
-      <c r="H14" s="33">
+      <c r="G14" s="48">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="50">
         <v>0.4</v>
       </c>
-      <c r="I14" s="28">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29">
-        <v>0</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N14" s="33">
+      <c r="I14" s="26">
+        <v>0</v>
+      </c>
+      <c r="J14" s="39">
+        <v>0</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="50">
         <v>0.5</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="51">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="77"/>
+    <row r="15" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="61"/>
       <c r="B15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="24">
         <v>4</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="48">
         <v>3.125</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="49">
         <v>3.125</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="39">
+        <v>0</v>
+      </c>
+      <c r="G15" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="50">
+        <v>2</v>
+      </c>
+      <c r="I15" s="26">
+        <v>32.5</v>
+      </c>
+      <c r="J15" s="39">
+        <v>3.75</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="50">
+        <v>0</v>
+      </c>
+      <c r="O15" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="62"/>
+      <c r="B16" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="25">
+        <v>10</v>
+      </c>
+      <c r="D16" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="42">
+        <v>0</v>
+      </c>
+      <c r="G16" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="54">
+        <v>0.3</v>
+      </c>
+      <c r="I16" s="43">
+        <v>100.7</v>
+      </c>
+      <c r="J16" s="42">
+        <v>8.1</v>
+      </c>
+      <c r="K16" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="54">
+        <v>0</v>
+      </c>
+      <c r="O16" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="6" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="59"/>
+      <c r="B17" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="31">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="33">
+      <c r="C17" s="33">
+        <v>133</v>
+      </c>
+      <c r="D17" s="56">
         <v>2</v>
       </c>
-      <c r="I15" s="28">
-        <v>32.5</v>
-      </c>
-      <c r="J15" s="29">
-        <v>3.75</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N15" s="33">
-        <v>0</v>
-      </c>
-      <c r="O15" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="78"/>
-      <c r="B16" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="48">
-        <v>10</v>
-      </c>
-      <c r="D16" s="35">
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="37">
-        <v>0.3</v>
-      </c>
-      <c r="I16" s="38">
-        <v>100.7</v>
-      </c>
-      <c r="J16" s="39">
-        <v>8.1</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="N16" s="37">
-        <v>0</v>
-      </c>
-      <c r="O16" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="69"/>
-      <c r="B17" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="71">
-        <v>133</v>
-      </c>
-      <c r="D17" s="49">
+      <c r="E17" s="56">
         <v>2</v>
       </c>
-      <c r="E17" s="49">
-        <v>2</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="49">
+      <c r="F17" s="56">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="56">
         <v>1.1278195488721805</v>
       </c>
-      <c r="H17" s="49">
+      <c r="H17" s="56">
         <v>0.45112781954887216</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="56">
         <v>90.225563909774436</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="56">
         <v>1.1278195488721805</v>
       </c>
-      <c r="K17" s="49">
+      <c r="K17" s="56">
         <v>0.01</v>
       </c>
-      <c r="L17" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="N17" s="50">
+      <c r="L17" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="57">
         <v>0.15037593984962405</v>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="58">
         <v>0.22556390977443608</v>
       </c>
       <c r="P17" s="7"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="41"/>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="59"/>
       <c r="E18" s="13"/>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="C19" s="15"/>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
       <c r="C21" s="16"/>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A17:A18"/>
@@ -2142,8 +2219,8 @@
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="0.65"/>
-        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="$F$17/2"/>
+        <cfvo type="formula" val="$F$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF00B050"/>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{390E8B1D-AD65-4E72-9311-9F292F9257FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64746FF5-2D82-47A4-A3FF-9FCE23C6A99B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A27705-D673-48F7-8638-8AE3A4254C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>Varieties released</t>
   </si>
   <si>
-    <t>Annual rate of genetic gain, by crop (%)</t>
-  </si>
-  <si>
     <t>Breeding</t>
   </si>
   <si>
@@ -152,6 +149,9 @@
   <si>
     <t xml:space="preserve">FTE - Number of staff
 </t>
+  </si>
+  <si>
+    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1413,9 @@
     <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="4.44140625" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="5.88671875" style="1" customWidth="1"/>
-    <col min="9" max="15" width="5.88671875" style="4" customWidth="1"/>
+    <col min="9" max="11" width="5.88671875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" style="4" customWidth="1"/>
+    <col min="13" max="15" width="5.88671875" style="4" customWidth="1"/>
     <col min="16" max="16" width="8.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1438,7 +1440,7 @@
     <row r="2" spans="1:16" s="21" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="76"/>
       <c r="B2" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="70" t="s">
@@ -1465,52 +1467,52 @@
       <c r="A3" s="76"/>
       <c r="B3" s="3"/>
       <c r="C3" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="H3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="29" t="s">
         <v>17</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>18</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="29" t="s">
         <v>20</v>
-      </c>
-      <c r="O3" s="29" t="s">
-        <v>21</v>
       </c>
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="23">
         <v>7</v>
@@ -1537,13 +1539,13 @@
         <v>26.285714285714285</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N4" s="37">
         <v>0.14285714285714285</v>
@@ -1555,7 +1557,7 @@
     <row r="5" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64"/>
       <c r="B5" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="24">
         <v>23</v>
@@ -1586,10 +1588,10 @@
         <v>2</v>
       </c>
       <c r="L5" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M5" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N5" s="26">
         <v>0.34782608695652173</v>
@@ -1601,7 +1603,7 @@
     <row r="6" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="64"/>
       <c r="B6" s="17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="24">
         <v>4</v>
@@ -1628,13 +1630,13 @@
         <v>28.25</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N6" s="26">
         <v>0</v>
@@ -1646,7 +1648,7 @@
     <row r="7" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="65"/>
       <c r="B7" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="25">
         <v>15</v>
@@ -1673,13 +1675,13 @@
         <v>20.6</v>
       </c>
       <c r="K7" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M7" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N7" s="43">
         <v>1.1333333333333333</v>
@@ -1690,10 +1692,10 @@
     </row>
     <row r="8" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="23">
         <v>12</v>
@@ -1720,13 +1722,13 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M8" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" s="37">
         <v>0.5</v>
@@ -1738,7 +1740,7 @@
     <row r="9" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64"/>
       <c r="B9" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="24">
         <v>20</v>
@@ -1765,13 +1767,13 @@
         <v>11.65</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M9" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="26">
         <v>0.05</v>
@@ -1783,7 +1785,7 @@
     <row r="10" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="64"/>
       <c r="B10" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="24">
         <v>7</v>
@@ -1810,13 +1812,13 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M10" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" s="26">
         <v>1.4285714285714286</v>
@@ -1828,7 +1830,7 @@
     <row r="11" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="65"/>
       <c r="B11" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="25">
         <v>4</v>
@@ -1855,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M11" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N11" s="43">
         <v>0.75</v>
@@ -1872,10 +1874,10 @@
     </row>
     <row r="12" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="23">
         <v>11</v>
@@ -1902,13 +1904,13 @@
         <v>9.9090909090909083</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M12" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N12" s="46">
         <v>0</v>
@@ -1920,7 +1922,7 @@
     <row r="13" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61"/>
       <c r="B13" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="24">
         <v>11</v>
@@ -1947,13 +1949,13 @@
         <v>14.181818181818182</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N13" s="50">
         <v>0.22727272727272727</v>
@@ -1965,7 +1967,7 @@
     <row r="14" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="61"/>
       <c r="B14" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="24">
         <v>5</v>
@@ -1992,13 +1994,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M14" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" s="50">
         <v>0.5</v>
@@ -2010,7 +2012,7 @@
     <row r="15" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="61"/>
       <c r="B15" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="24">
         <v>4</v>
@@ -2037,13 +2039,13 @@
         <v>3.75</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M15" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N15" s="50">
         <v>0</v>
@@ -2055,7 +2057,7 @@
     <row r="16" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="62"/>
       <c r="B16" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="25">
         <v>10</v>
@@ -2082,13 +2084,13 @@
         <v>8.1</v>
       </c>
       <c r="K16" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M16" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N16" s="54">
         <v>0</v>
@@ -2100,7 +2102,7 @@
     <row r="17" spans="1:16" s="6" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="59"/>
       <c r="B17" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="33">
         <v>133</v>
@@ -2130,10 +2132,10 @@
         <v>0.01</v>
       </c>
       <c r="L17" s="56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M17" s="56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N17" s="57">
         <v>0.15037593984962405</v>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A27705-D673-48F7-8638-8AE3A4254C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{390E8B1D-AD65-4E72-9311-9F292F9257FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C2D13CF-416A-4BF4-AD88-44041BEC0A40}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$A$1:$O$17</definedName>
@@ -60,6 +57,9 @@
     <t>Varieties released</t>
   </si>
   <si>
+    <t>Annual rate of genetic gain, by crop (%)</t>
+  </si>
+  <si>
     <t>Breeding</t>
   </si>
   <si>
@@ -149,9 +149,6 @@
   <si>
     <t xml:space="preserve">FTE - Number of staff
 </t>
-  </si>
-  <si>
-    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -245,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -318,17 +315,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -572,28 +558,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -702,12 +666,125 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -729,12 +806,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -747,13 +818,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -762,8 +833,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -771,158 +845,182 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,148 +1039,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="PR 1"/>
-      <sheetName val="PR 2"/>
-      <sheetName val="PR 3"/>
-      <sheetName val="PR 4"/>
-      <sheetName val="PR 5"/>
-      <sheetName val="PR 6"/>
-      <sheetName val="PR 7"/>
-      <sheetName val="PR 8"/>
-      <sheetName val="PR 9"/>
-      <sheetName val="PR 10"/>
-      <sheetName val="PR 11"/>
-      <sheetName val="PR 12"/>
-      <sheetName val="PR 13"/>
-      <sheetName val="PR 14"/>
-      <sheetName val="PR15"/>
-      <sheetName val="PR 16"/>
-      <sheetName val="PR 18"/>
-      <sheetName val="PR 19"/>
-      <sheetName val="PR20"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="G3">
-            <v>3.1428571428571428</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="G3">
-            <v>0.44795918367346937</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="3">
-          <cell r="G3">
-            <v>0.14285714285714285</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="3">
-          <cell r="G3">
-            <v>0.14285714285714285</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="3">
-          <cell r="G3">
-            <v>0.14285714285714285</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="3">
-          <cell r="G3">
-            <v>9.7142857142857135</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="3">
-          <cell r="G3">
-            <v>26.285714285714285</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="4">
-          <cell r="G4">
-            <v>2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
-        <row r="5">
-          <cell r="G5">
-            <v>0.25</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="3">
-          <cell r="G3">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="6">
-          <cell r="G6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
-        <row r="3">
-          <cell r="G3">
-            <v>0.14285714285714285</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
-        <row r="4">
-          <cell r="G4">
-            <v>8.6956521739130432E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="17">
-        <row r="4">
-          <cell r="G4">
-            <v>4.3478260869565216E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="18">
-        <row r="4">
-          <cell r="G4">
-            <v>8.6956521739130432E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1411,754 +1367,752 @@
   <cols>
     <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="5.88671875" style="1" customWidth="1"/>
-    <col min="9" max="11" width="5.88671875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="4" customWidth="1"/>
-    <col min="13" max="15" width="5.88671875" style="4" customWidth="1"/>
+    <col min="9" max="15" width="5.88671875" style="4" customWidth="1"/>
     <col min="16" max="16" width="8.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="69"/>
+      <c r="B1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:16" s="21" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
-      <c r="B2" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="70" t="s">
+    <row r="2" spans="1:16" s="19" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="83"/>
+      <c r="B2" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="73" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="73" t="s">
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="20"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="1:16" s="5" customFormat="1" ht="108.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="76"/>
+      <c r="A3" s="83"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="C3" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="F3" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="G3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="I3" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="J3" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="11" t="s">
+      <c r="L3" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="N3" s="58" t="s">
         <v>20</v>
+      </c>
+      <c r="O3" s="59" t="s">
+        <v>21</v>
       </c>
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="23">
-        <v>7</v>
-      </c>
-      <c r="D4" s="34">
-        <v>3.1428571428571428</v>
-      </c>
-      <c r="E4" s="35">
-        <v>3.1357142857142857</v>
-      </c>
-      <c r="F4" s="36">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="G4" s="34">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="H4" s="37">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="I4" s="37">
-        <v>9.7142857142857135</v>
-      </c>
-      <c r="J4" s="36">
-        <v>26.285714285714285</v>
-      </c>
-      <c r="K4" s="34" t="s">
+      <c r="A4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="37">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="O4" s="36">
+      <c r="C4" s="21">
+        <v>4</v>
+      </c>
+      <c r="D4" s="30">
+        <v>5.5</v>
+      </c>
+      <c r="E4" s="31">
+        <v>0.78392857142857142</v>
+      </c>
+      <c r="F4" s="61">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="I4" s="33">
+        <v>17</v>
+      </c>
+      <c r="J4" s="32">
+        <v>46</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="O4" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="64"/>
-      <c r="B5" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="24">
-        <v>23</v>
-      </c>
-      <c r="D5" s="22">
-        <v>2.2391304347826089</v>
-      </c>
-      <c r="E5" s="38">
-        <v>2.2369565217391307</v>
-      </c>
-      <c r="F5" s="39">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>1.0434782608695652</v>
-      </c>
-      <c r="H5" s="26">
-        <v>1.2173913043478262</v>
-      </c>
-      <c r="I5" s="26">
-        <v>4.6956521739130439</v>
-      </c>
-      <c r="J5" s="39">
-        <v>9.304347826086957</v>
-      </c>
-      <c r="K5" s="22">
-        <f>'[1]PR 8'!$G$4</f>
-        <v>2</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="26">
-        <v>0.34782608695652173</v>
-      </c>
-      <c r="O5" s="39">
-        <v>0.21739130434782608</v>
+      <c r="A5" s="71"/>
+      <c r="B5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="22">
+        <v>24</v>
+      </c>
+      <c r="D5" s="20">
+        <v>2.1458333333333335</v>
+      </c>
+      <c r="E5" s="34">
+        <v>9.3206521739130452E-2</v>
+      </c>
+      <c r="F5" s="62">
+        <v>0</v>
+      </c>
+      <c r="G5" s="20">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="I5" s="24">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="35">
+        <v>8.9166666666666661</v>
+      </c>
+      <c r="K5" s="20">
+        <v>1.9166666666666667</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O5" s="35">
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64"/>
-      <c r="B6" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="24">
-        <v>4</v>
-      </c>
-      <c r="D6" s="22">
-        <v>1.25</v>
-      </c>
-      <c r="E6" s="38">
-        <v>1.25</v>
-      </c>
-      <c r="F6" s="39">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22">
-        <v>6.5</v>
-      </c>
-      <c r="H6" s="26">
-        <v>4.75</v>
-      </c>
-      <c r="I6" s="26">
-        <v>1.25</v>
-      </c>
-      <c r="J6" s="39">
-        <v>28.25</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" s="26">
-        <v>0</v>
-      </c>
-      <c r="O6" s="39">
+      <c r="A6" s="71"/>
+      <c r="B6" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="22">
+        <v>5</v>
+      </c>
+      <c r="D6" s="20">
+        <v>1</v>
+      </c>
+      <c r="E6" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="62">
+        <v>0</v>
+      </c>
+      <c r="G6" s="20">
+        <v>5.2</v>
+      </c>
+      <c r="H6" s="24">
+        <v>3.8</v>
+      </c>
+      <c r="I6" s="24">
+        <v>1</v>
+      </c>
+      <c r="J6" s="35">
+        <v>22.6</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="24">
+        <v>0</v>
+      </c>
+      <c r="O6" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="65"/>
-      <c r="B7" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="25">
-        <v>15</v>
-      </c>
-      <c r="D7" s="40">
-        <v>1.0266666666666666</v>
-      </c>
-      <c r="E7" s="41">
-        <v>1.0266666666666666</v>
-      </c>
-      <c r="F7" s="42">
-        <v>0</v>
-      </c>
-      <c r="G7" s="40">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="H7" s="43">
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="I7" s="43">
-        <v>149.80000000000001</v>
-      </c>
-      <c r="J7" s="42">
-        <v>20.6</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="43">
-        <v>1.1333333333333333</v>
-      </c>
-      <c r="O7" s="42">
-        <v>0.13333333333333333</v>
+      <c r="A7" s="72"/>
+      <c r="B7" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="23">
+        <v>16</v>
+      </c>
+      <c r="D7" s="36">
+        <v>0.96250000000000002</v>
+      </c>
+      <c r="E7" s="37">
+        <v>6.4166666666666664E-2</v>
+      </c>
+      <c r="F7" s="63">
+        <v>0</v>
+      </c>
+      <c r="G7" s="36">
+        <v>0.3125</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0.4375</v>
+      </c>
+      <c r="I7" s="39">
+        <v>140.4375</v>
+      </c>
+      <c r="J7" s="38">
+        <v>19.3125</v>
+      </c>
+      <c r="K7" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="39">
+        <v>1.0625</v>
+      </c>
+      <c r="O7" s="38">
+        <v>0.125</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="63" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="23">
-        <v>12</v>
-      </c>
-      <c r="D8" s="34">
-        <v>3.4541666666666671</v>
-      </c>
-      <c r="E8" s="35">
-        <v>3.4541666666666671</v>
-      </c>
-      <c r="F8" s="36">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="G8" s="34">
-        <v>0.75</v>
-      </c>
-      <c r="H8" s="37">
-        <v>0.75</v>
-      </c>
-      <c r="I8" s="37">
-        <v>8.5</v>
-      </c>
-      <c r="J8" s="36">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="O8" s="36">
-        <v>0.16666666666666666</v>
+      <c r="A8" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="21">
+        <v>21</v>
+      </c>
+      <c r="D8" s="30">
+        <v>0.99380952380952381</v>
+      </c>
+      <c r="E8" s="31">
+        <v>0.16448412698412701</v>
+      </c>
+      <c r="F8" s="61">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="G8" s="30">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H8" s="33">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="I8" s="33">
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="J8" s="32">
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="33">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="O8" s="32">
+        <v>9.5238095238095233E-2</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64"/>
-      <c r="B9" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="24">
-        <v>20</v>
-      </c>
-      <c r="D9" s="22">
-        <v>1.0435000000000001</v>
-      </c>
-      <c r="E9" s="38">
-        <v>1.0435000000000001</v>
-      </c>
-      <c r="F9" s="39">
-        <v>4.1499999999999995E-2</v>
-      </c>
-      <c r="G9" s="22">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H9" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="I9" s="26">
-        <v>159.25</v>
-      </c>
-      <c r="J9" s="39">
-        <v>11.65</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="26">
-        <v>0.05</v>
-      </c>
-      <c r="O9" s="39">
-        <v>0.45</v>
+      <c r="A9" s="71"/>
+      <c r="B9" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="22">
+        <v>13</v>
+      </c>
+      <c r="D9" s="20">
+        <v>3.1884615384615387</v>
+      </c>
+      <c r="E9" s="34">
+        <v>8.0269230769230773E-2</v>
+      </c>
+      <c r="F9" s="62">
+        <v>6.3846153846153844E-2</v>
+      </c>
+      <c r="G9" s="20">
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="H9" s="24">
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="I9" s="24">
+        <v>245</v>
+      </c>
+      <c r="J9" s="35">
+        <v>17.923076923076923</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="24">
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="O9" s="35">
+        <v>0.69230769230769229</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
-      <c r="B10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="24">
-        <v>7</v>
-      </c>
-      <c r="D10" s="22">
-        <v>2.2142857142857144</v>
-      </c>
-      <c r="E10" s="38">
-        <v>2.2142857142857144</v>
-      </c>
-      <c r="F10" s="39">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G10" s="22">
-        <v>1</v>
-      </c>
-      <c r="H10" s="26">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="I10" s="26">
-        <v>536.28571428571433</v>
-      </c>
-      <c r="J10" s="39">
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" s="26">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="O10" s="39">
-        <v>0.2857142857142857</v>
+      <c r="A10" s="71"/>
+      <c r="B10" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="22">
+        <v>8</v>
+      </c>
+      <c r="D10" s="20">
+        <v>1.9375</v>
+      </c>
+      <c r="E10" s="34">
+        <v>0.2767857142857143</v>
+      </c>
+      <c r="F10" s="62">
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="I10" s="24">
+        <v>469.25</v>
+      </c>
+      <c r="J10" s="35">
+        <v>2.5</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="24">
+        <v>1.25</v>
+      </c>
+      <c r="O10" s="35">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="65"/>
-      <c r="B11" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="25">
-        <v>4</v>
-      </c>
-      <c r="D11" s="40">
-        <v>0</v>
-      </c>
-      <c r="E11" s="41">
-        <v>0</v>
-      </c>
-      <c r="F11" s="42">
-        <v>0</v>
-      </c>
-      <c r="G11" s="40">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="43">
-        <v>0.25</v>
-      </c>
-      <c r="I11" s="43">
-        <v>0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0</v>
-      </c>
-      <c r="K11" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="43">
-        <v>0.75</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.75</v>
+      <c r="A11" s="72"/>
+      <c r="B11" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="23">
+        <v>5</v>
+      </c>
+      <c r="D11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="63">
+        <v>0</v>
+      </c>
+      <c r="G11" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0.2</v>
+      </c>
+      <c r="I11" s="39">
+        <v>0</v>
+      </c>
+      <c r="J11" s="38">
+        <v>0</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="39">
+        <v>0.6</v>
+      </c>
+      <c r="O11" s="38">
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="23">
-        <v>11</v>
-      </c>
-      <c r="D12" s="44">
-        <v>0.90181818181818185</v>
-      </c>
-      <c r="E12" s="45">
-        <v>0.90181818181818185</v>
-      </c>
-      <c r="F12" s="36">
-        <v>0</v>
-      </c>
-      <c r="G12" s="44">
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="H12" s="46">
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="I12" s="37">
-        <v>8.545454545454545</v>
-      </c>
-      <c r="J12" s="36">
-        <v>9.9090909090909083</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="46">
-        <v>0</v>
-      </c>
-      <c r="O12" s="47">
+      <c r="A12" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="21">
+        <v>12</v>
+      </c>
+      <c r="D12" s="40">
+        <v>0.82666666666666666</v>
+      </c>
+      <c r="E12" s="41">
+        <v>7.515151515151515E-2</v>
+      </c>
+      <c r="F12" s="61">
+        <v>0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H12" s="42">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I12" s="33">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="J12" s="32">
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="42">
+        <v>0</v>
+      </c>
+      <c r="O12" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61"/>
-      <c r="B13" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="24">
+      <c r="A13" s="68"/>
+      <c r="B13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="22">
         <v>11</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="44">
         <v>0.6</v>
       </c>
-      <c r="E13" s="49">
-        <v>0.6</v>
-      </c>
-      <c r="F13" s="39">
-        <v>0</v>
-      </c>
-      <c r="G13" s="48">
+      <c r="E13" s="45">
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="F13" s="62">
+        <v>0</v>
+      </c>
+      <c r="G13" s="44">
         <v>0.36363636363636365</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="46">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="24">
         <v>173.81818181818181</v>
       </c>
-      <c r="J13" s="39">
+      <c r="J13" s="35">
         <v>14.181818181818182</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N13" s="50">
+      <c r="K13" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="46">
         <v>0.22727272727272727</v>
       </c>
-      <c r="O13" s="51">
+      <c r="O13" s="47">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="61"/>
-      <c r="B14" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="24">
+      <c r="A14" s="68"/>
+      <c r="B14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="22">
         <v>5</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="44">
         <v>2.6659999999999999</v>
       </c>
-      <c r="E14" s="49">
-        <v>2.6659999999999999</v>
-      </c>
-      <c r="F14" s="39">
+      <c r="E14" s="45">
+        <v>0.53320000000000001</v>
+      </c>
+      <c r="F14" s="62">
         <v>0.2</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="44">
         <v>0.2</v>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="46">
         <v>0.4</v>
       </c>
-      <c r="I14" s="26">
-        <v>0</v>
-      </c>
-      <c r="J14" s="39">
-        <v>0</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="50">
+      <c r="I14" s="24">
+        <v>0</v>
+      </c>
+      <c r="J14" s="35">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="46">
         <v>0.5</v>
       </c>
-      <c r="O14" s="51">
+      <c r="O14" s="47">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="61"/>
-      <c r="B15" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="24">
-        <v>4</v>
+    <row r="15" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="68"/>
+      <c r="B15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="22">
+        <v>6</v>
       </c>
       <c r="D15" s="48">
-        <v>3.125</v>
+        <v>2.0833333333333335</v>
       </c>
       <c r="E15" s="49">
-        <v>3.125</v>
-      </c>
-      <c r="F15" s="39">
-        <v>0</v>
-      </c>
-      <c r="G15" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="50">
-        <v>2</v>
-      </c>
-      <c r="I15" s="26">
-        <v>32.5</v>
-      </c>
-      <c r="J15" s="39">
-        <v>3.75</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="50">
-        <v>0</v>
-      </c>
-      <c r="O15" s="51">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F15" s="63">
+        <v>0</v>
+      </c>
+      <c r="G15" s="44">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H15" s="46">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="I15" s="24">
+        <v>21.666666666666668</v>
+      </c>
+      <c r="J15" s="35">
+        <v>2.5</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="46">
+        <v>0</v>
+      </c>
+      <c r="O15" s="47">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="62"/>
-      <c r="B16" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="25">
-        <v>10</v>
-      </c>
-      <c r="D16" s="52">
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="53">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="42">
-        <v>0</v>
-      </c>
-      <c r="G16" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="54">
-        <v>0.3</v>
-      </c>
-      <c r="I16" s="43">
-        <v>100.7</v>
-      </c>
-      <c r="J16" s="42">
-        <v>8.1</v>
-      </c>
-      <c r="K16" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="54">
-        <v>0</v>
-      </c>
-      <c r="O16" s="55">
+      <c r="A16" s="69"/>
+      <c r="B16" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="23">
+        <v>11</v>
+      </c>
+      <c r="D16" s="55">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="E16" s="56">
+        <v>2.7272727272727271E-2</v>
+      </c>
+      <c r="F16" s="64">
+        <v>0</v>
+      </c>
+      <c r="G16" s="48">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="H16" s="50">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="I16" s="39">
+        <v>91.545454545454547</v>
+      </c>
+      <c r="J16" s="38">
+        <v>7.3636363636363633</v>
+      </c>
+      <c r="K16" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="50">
+        <v>0</v>
+      </c>
+      <c r="O16" s="51">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="6" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="59"/>
-      <c r="B17" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="33">
-        <v>133</v>
-      </c>
-      <c r="D17" s="56">
+      <c r="A17" s="66"/>
+      <c r="B17" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="29">
+        <f>SUM(C4:C16)</f>
+        <v>141</v>
+      </c>
+      <c r="D17" s="52">
         <v>2</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="52">
         <v>2</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="52">
         <v>0.01</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="52">
         <v>1.1278195488721805</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="52">
         <v>0.45112781954887216</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="52">
         <v>90.225563909774436</v>
       </c>
-      <c r="J17" s="56">
+      <c r="J17" s="52">
         <v>1.1278195488721805</v>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="52">
         <v>0.01</v>
       </c>
-      <c r="L17" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" s="57">
+      <c r="L17" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="53">
         <v>0.15037593984962405</v>
       </c>
-      <c r="O17" s="58">
+      <c r="O17" s="54">
         <v>0.22556390977443608</v>
       </c>
       <c r="P17" s="7"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="66"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
-      <c r="C19" s="15"/>
+      <c r="C19" s="13"/>
     </row>
     <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9"/>
     </row>
     <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
-      <c r="C21" s="16"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2174,7 +2128,7 @@
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="164">
+    <cfRule type="colorScale" priority="167">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -2186,7 +2140,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="165">
+    <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2196,7 +2150,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="166">
+    <cfRule type="colorScale" priority="169">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2206,7 +2160,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="167">
+    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2218,7 +2172,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2230,7 +2184,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="171">
+    <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2240,7 +2194,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="172">
+    <cfRule type="colorScale" priority="175">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2250,7 +2204,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="173">
+    <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2262,7 +2216,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H16">
-    <cfRule type="colorScale" priority="174">
+    <cfRule type="colorScale" priority="177">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$H$17/2"/>
@@ -2274,7 +2228,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="175">
+    <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2284,7 +2238,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="176">
+    <cfRule type="colorScale" priority="179">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2296,7 +2250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="177">
+    <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2306,7 +2260,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="178">
+    <cfRule type="colorScale" priority="181">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2317,8 +2271,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="179">
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="0.65"/>
@@ -2329,8 +2283,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M5 L4:L16">
-    <cfRule type="colorScale" priority="15">
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="182">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="0.65"/>
@@ -2341,8 +2295,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K7">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:K16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M5 L4:L16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.65"/>
+        <cfvo type="formula" val="0.65"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M6">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$N$17/2"/>
@@ -2352,7 +2342,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2362,7 +2352,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2374,7 +2364,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M16">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="0.65"/>
@@ -2386,7 +2376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N16">
-    <cfRule type="colorScale" priority="181">
+    <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$N$17/2"/>
@@ -2396,7 +2386,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="182">
+    <cfRule type="colorScale" priority="185">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2406,7 +2396,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="183">
+    <cfRule type="colorScale" priority="186">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2418,7 +2408,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O16">
-    <cfRule type="colorScale" priority="184">
+    <cfRule type="colorScale" priority="187">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$O$17/2"/>
@@ -2428,7 +2418,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="185">
+    <cfRule type="colorScale" priority="188">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2438,7 +2428,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="186">
+    <cfRule type="colorScale" priority="189">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2448,7 +2438,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="187">
+    <cfRule type="colorScale" priority="190">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2458,7 +2448,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="188">
+    <cfRule type="colorScale" priority="191">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>

--- a/data/Heat map 2.xlsx
+++ b/data/Heat map 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{390E8B1D-AD65-4E72-9311-9F292F9257FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C2D13CF-416A-4BF4-AD88-44041BEC0A40}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{390E8B1D-AD65-4E72-9311-9F292F9257FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91999F50-B08F-4EF4-B251-80F65F16EEE4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7854C689-FBEF-4104-AB78-E5B5C107CDEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -156,8 +156,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -782,21 +782,21 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -806,7 +806,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -827,25 +827,16 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -858,88 +849,85 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -954,16 +942,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1022,6 +1010,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1363,758 +1363,758 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="5.88671875" style="1" customWidth="1"/>
-    <col min="9" max="15" width="5.88671875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="8.21875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.90625" style="1" customWidth="1"/>
+    <col min="9" max="15" width="5.90625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="8.1796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="72"/>
     </row>
-    <row r="2" spans="1:16" s="19" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="83"/>
+    <row r="2" spans="1:16" s="19" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="79"/>
       <c r="B2" s="16" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="17"/>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="80" t="s">
+      <c r="E2" s="74"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="80" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="82"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="78"/>
       <c r="P2" s="18"/>
     </row>
-    <row r="3" spans="1:16" s="5" customFormat="1" ht="108.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="83"/>
+    <row r="3" spans="1:16" s="5" customFormat="1" ht="108.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="79"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="58" t="s">
+      <c r="H3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="65" t="s">
+      <c r="L3" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="65" t="s">
+      <c r="M3" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="N3" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="55" t="s">
         <v>21</v>
       </c>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70" t="s">
+    <row r="4" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="80">
         <v>4</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="26">
         <v>5.5</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="27">
         <v>0.78392857142857142</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="57">
         <v>0.25</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="26">
         <v>0.25</v>
       </c>
-      <c r="H4" s="33">
+      <c r="H4" s="29">
         <v>0.25</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="29">
         <v>17</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="28">
         <v>46</v>
       </c>
-      <c r="K4" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="33">
+      <c r="K4" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="29">
         <v>0.25</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="28">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="71"/>
+    <row r="5" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="67"/>
       <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="81">
         <v>24</v>
       </c>
       <c r="D5" s="20">
         <v>2.1458333333333335</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="30">
         <v>9.3206521739130452E-2</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="58">
         <v>0</v>
       </c>
       <c r="G5" s="20">
         <v>1</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="21">
         <v>1.1666666666666667</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="21">
         <v>4.5</v>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="31">
         <v>8.9166666666666661</v>
       </c>
       <c r="K5" s="20">
         <v>1.9166666666666667</v>
       </c>
-      <c r="L5" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="24">
+      <c r="L5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="21">
         <v>0.33333333333333331</v>
       </c>
-      <c r="O5" s="35">
+      <c r="O5" s="31">
         <v>0.20833333333333334</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
+    <row r="6" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="67"/>
       <c r="B6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="81">
         <v>5</v>
       </c>
       <c r="D6" s="20">
         <v>1</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="30">
         <v>0.25</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="58">
         <v>0</v>
       </c>
       <c r="G6" s="20">
         <v>5.2</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="21">
         <v>3.8</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="21">
         <v>1</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="31">
         <v>22.6</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="24">
-        <v>0</v>
-      </c>
-      <c r="O6" s="35">
+      <c r="L6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="21">
+        <v>0</v>
+      </c>
+      <c r="O6" s="31">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="72"/>
-      <c r="B7" s="27" t="s">
+    <row r="7" spans="1:16" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="68"/>
+      <c r="B7" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="82">
         <v>16</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="32">
         <v>0.96250000000000002</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="33">
         <v>6.4166666666666664E-2</v>
       </c>
-      <c r="F7" s="63">
-        <v>0</v>
-      </c>
-      <c r="G7" s="36">
+      <c r="F7" s="59">
+        <v>0</v>
+      </c>
+      <c r="G7" s="32">
         <v>0.3125</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="35">
         <v>0.4375</v>
       </c>
-      <c r="I7" s="39">
+      <c r="I7" s="35">
         <v>140.4375</v>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="34">
         <v>19.3125</v>
       </c>
-      <c r="K7" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" s="39">
+      <c r="K7" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="35">
         <v>1.0625</v>
       </c>
-      <c r="O7" s="38">
+      <c r="O7" s="34">
         <v>0.125</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="70" t="s">
+    <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="80">
         <v>21</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <v>0.99380952380952381</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="27">
         <v>0.16448412698412701</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="57">
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="26">
         <v>0.42857142857142855</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="29">
         <v>0.42857142857142855</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="29">
         <v>4.8571428571428568</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="28">
         <v>0.47619047619047616</v>
       </c>
-      <c r="K8" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="33">
+      <c r="K8" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="29">
         <v>0.2857142857142857</v>
       </c>
-      <c r="O8" s="32">
+      <c r="O8" s="28">
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
+    <row r="9" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="67"/>
       <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="81">
         <v>13</v>
       </c>
       <c r="D9" s="20">
         <v>3.1884615384615387</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="30">
         <v>8.0269230769230773E-2</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="58">
         <v>6.3846153846153844E-2</v>
       </c>
       <c r="G9" s="20">
         <v>1.6923076923076923</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="21">
         <v>1.0769230769230769</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="21">
         <v>245</v>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="31">
         <v>17.923076923076923</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" s="24">
+      <c r="L9" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="21">
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="O9" s="35">
+      <c r="O9" s="31">
         <v>0.69230769230769229</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
+    <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="67"/>
       <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="81">
         <v>8</v>
       </c>
       <c r="D10" s="20">
         <v>1.9375</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="30">
         <v>0.2767857142857143</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="58">
         <v>0.25</v>
       </c>
       <c r="G10" s="20">
         <v>0.875</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="21">
         <v>0.375</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="21">
         <v>469.25</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="31">
         <v>2.5</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" s="24">
+      <c r="L10" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="21">
         <v>1.25</v>
       </c>
-      <c r="O10" s="35">
+      <c r="O10" s="31">
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="72"/>
-      <c r="B11" s="27" t="s">
+    <row r="11" spans="1:16" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="68"/>
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="82">
         <v>5</v>
       </c>
-      <c r="D11" s="36">
-        <v>0</v>
-      </c>
-      <c r="E11" s="37">
-        <v>0</v>
-      </c>
-      <c r="F11" s="63">
-        <v>0</v>
-      </c>
-      <c r="G11" s="36">
+      <c r="D11" s="32">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33">
+        <v>0</v>
+      </c>
+      <c r="F11" s="59">
+        <v>0</v>
+      </c>
+      <c r="G11" s="32">
         <v>0.4</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="35">
         <v>0.2</v>
       </c>
-      <c r="I11" s="39">
-        <v>0</v>
-      </c>
-      <c r="J11" s="38">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="39">
+      <c r="I11" s="35">
+        <v>0</v>
+      </c>
+      <c r="J11" s="34">
+        <v>0</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="35">
         <v>0.6</v>
       </c>
-      <c r="O11" s="38">
+      <c r="O11" s="34">
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67" t="s">
+    <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="80">
         <v>12</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="36">
         <v>0.82666666666666666</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="37">
         <v>7.515151515151515E-2</v>
       </c>
-      <c r="F12" s="61">
-        <v>0</v>
-      </c>
-      <c r="G12" s="40">
+      <c r="F12" s="57">
+        <v>0</v>
+      </c>
+      <c r="G12" s="36">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="38">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="29">
         <v>7.833333333333333</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="28">
         <v>9.0833333333333339</v>
       </c>
-      <c r="K12" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="42">
-        <v>0</v>
-      </c>
-      <c r="O12" s="43">
+      <c r="K12" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="38">
+        <v>0</v>
+      </c>
+      <c r="O12" s="39">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="68"/>
+    <row r="13" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="64"/>
       <c r="B13" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="81">
         <v>11</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="40">
         <v>0.6</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="41">
         <v>5.4545454545454543E-2</v>
       </c>
-      <c r="F13" s="62">
-        <v>0</v>
-      </c>
-      <c r="G13" s="44">
+      <c r="F13" s="58">
+        <v>0</v>
+      </c>
+      <c r="G13" s="40">
         <v>0.36363636363636365</v>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="42">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="21">
         <v>173.81818181818181</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="31">
         <v>14.181818181818182</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="46">
+      <c r="L13" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="42">
         <v>0.22727272727272727</v>
       </c>
-      <c r="O13" s="47">
+      <c r="O13" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="68"/>
+    <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="64"/>
       <c r="B14" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="81">
         <v>5</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="40">
         <v>2.6659999999999999</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="41">
         <v>0.53320000000000001</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F14" s="58">
         <v>0.2</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="40">
         <v>0.2</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="42">
         <v>0.4</v>
       </c>
-      <c r="I14" s="24">
-        <v>0</v>
-      </c>
-      <c r="J14" s="35">
+      <c r="I14" s="21">
+        <v>0</v>
+      </c>
+      <c r="J14" s="31">
         <v>0</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" s="46">
+      <c r="L14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="42">
         <v>0.5</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="68"/>
+    <row r="15" spans="1:16" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="64"/>
       <c r="B15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="81">
         <v>6</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="44">
         <v>2.0833333333333335</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="45">
         <v>0.52083333333333337</v>
       </c>
-      <c r="F15" s="63">
-        <v>0</v>
-      </c>
-      <c r="G15" s="44">
+      <c r="F15" s="59">
+        <v>0</v>
+      </c>
+      <c r="G15" s="40">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H15" s="46">
+      <c r="H15" s="42">
         <v>1.3333333333333333</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="21">
         <v>21.666666666666668</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="31">
         <v>2.5</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" s="46">
-        <v>0</v>
-      </c>
-      <c r="O15" s="47">
+      <c r="L15" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="42">
+        <v>0</v>
+      </c>
+      <c r="O15" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="69"/>
-      <c r="B16" s="27" t="s">
+    <row r="16" spans="1:16" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="65"/>
+      <c r="B16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="82">
         <v>11</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="51">
         <v>0.27272727272727271</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="52">
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="F16" s="64">
-        <v>0</v>
-      </c>
-      <c r="G16" s="48">
+      <c r="F16" s="60">
+        <v>0</v>
+      </c>
+      <c r="G16" s="44">
         <v>0.45454545454545453</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="46">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="35">
         <v>91.545454545454547</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16" s="34">
         <v>7.3636363636363633</v>
       </c>
-      <c r="K16" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" s="50">
-        <v>0</v>
-      </c>
-      <c r="O16" s="51">
+      <c r="K16" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="46">
+        <v>0</v>
+      </c>
+      <c r="O16" s="47">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="6" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="66"/>
-      <c r="B17" s="28" t="s">
+    <row r="17" spans="1:16" s="6" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="62"/>
+      <c r="B17" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="83">
         <f>SUM(C4:C16)</f>
         <v>141</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="48">
         <v>2</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="48">
         <v>2</v>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="48">
         <v>0.01</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="48">
         <v>1.1278195488721805</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="48">
         <v>0.45112781954887216</v>
       </c>
-      <c r="I17" s="52">
+      <c r="I17" s="48">
         <v>90.225563909774436</v>
       </c>
-      <c r="J17" s="52">
+      <c r="J17" s="48">
         <v>1.1278195488721805</v>
       </c>
-      <c r="K17" s="52">
+      <c r="K17" s="48">
         <v>0.01</v>
       </c>
-      <c r="L17" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" s="53">
+      <c r="L17" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="49">
         <v>0.15037593984962405</v>
       </c>
-      <c r="O17" s="54">
+      <c r="O17" s="50">
         <v>0.22556390977443608</v>
       </c>
       <c r="P17" s="7"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="66"/>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="62"/>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" s="9"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" s="10"/>
       <c r="C21" s="14"/>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A17:A18"/>
